--- a/reports/rag_chat/report.xlsx
+++ b/reports/rag_chat/report.xlsx
@@ -165,7 +165,7 @@
     <t>Run ID</t>
   </si>
   <si>
-    <t>01a0cc58-8c5d-7ea2-bbbc-02ba4ff3e085</t>
+    <t>01a0cce2-2de3-71b1-a3b6-5767197c0214</t>
   </si>
   <si>
     <t>Recording</t>
@@ -183,7 +183,7 @@
     <t>FX fetched at</t>
   </si>
   <si>
-    <t>2026-09-23T03:35:56.284466Z</t>
+    <t>2026-09-23T06:06:28.037095Z</t>
   </si>
   <si>
     <t>UTC</t>
@@ -306,7 +306,7 @@
     <t>gpt-5.6-luna</t>
   </si>
   <si>
-    <t>01a0cc58-8c61-7262-a785-e801c9cfbf9c</t>
+    <t>01a0cce2-2de7-7012-bcd4-719bc907d99e</t>
   </si>
   <si>
     <t>Fresh input</t>
@@ -345,8 +345,8 @@
     <t xml:space="preserve">    Output content</t>
   </si>
   <si>
-    <t>[{"id": "rs_0d44d690dddacab3006ab349df001087d297a59789e1aeed16", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs0nf0yvWiYLucKfY0HfpN6sErk8Tq74w6ODIj1PoJc-Df64rUsrlGweVf3jPMmBZV1WEn3GZWi3bim-F4R_EQeVPFYMQJ3nVYQBM14P12Ga-2QwvFdm8qlb0tS6VowpA6GJbLI9OrsSIviNEiZ3uV_DScgwT5Ss1hZXifX-yFQQuauw6l4jH8HnaXNoW5QaCd-NtQWrqLI7PweZQWqzH9B19ePAJmKh8G3kcklhTyRAarTgcU91gDxe3xw8j4Slad5zBBXrWIdcH3wWPy0BKuX5lwHgF3hH4hi2-ZEI5mHLkMCRV9zM6wDJuIHcrrYGdfKiH-azkKCK8WY-0dj8wEJBVfbmwEk9eMuVMREADm95Ku-B6ZkpAQXGN-JhE-R6FU1xEO_c-ckuxTk0VeIu8OANMZCIFVYMIWJJsugXjlQfeGby8B6JI0tLh11rAEk6wB27KRHtrtmjW0_RnVNmBgbfl32QLE9nvy-LSJhFK9hb_9O7PG9Pvt4Wx6W7iAQULalafW3q9P5BLn1kSogaIEdHViawKVdBEtXtEf7Pg3nnuJng_9zDuEz40rEc2BFd-hlZQylbwsvXo9emID4WYyZ9-Gntp-UTFTRXe7v1YKN41nleSKl2wlVAolNj8x8LhIwGmnWs2dKbbxjXqJC9ZDWuhiT-7WAB5GS1e766PC6cEQqu0NkNYdHg3xGdIftYDf63nR8vPNW7nE9zpikZfiVru_BCf0faaBnJk4cekGI0epfIvqax-Snoxe7w_RdOR-osxFRdJzha3grHL-48euAFi32hDfgJRVpEgND4H9R87l_7LM0Qu6jyF5o1HWpbIYMVRo9Es9xpfodGOO2a9x9AXRyQ6YXVAcbjQcMB_zz3UPftX7svcJDodmGvwJ734MkkjHreH-xhcVcKoXx7PXZjoxvVsIpEs5d56CcJVPSxhLJOx6_z4j2ohXHC2Stib1lRJbJLiAw0ER66kASFc2i7qlxKZJFZVh85ujQt6R7UGDHHyQm9OiZPcc5Ix_DfLr3fYljye6BOIuvQFl0mq7aIYBuiOl9ZWICf0MTMKv2BDMW5bWZLTi9n3AxG9_PpHFKmv3idLcwJnMyY72JXrQqd0OpcC1w6y5IaXqynN6CScvS8Hs6Jw2zHCK25c4mqqlLyukSGzx5FUzDHZv0OYgW3KfOpARNI-WBFE5TsI1EzQ9XgKoev2csKJIUnZPN_TIoDG"}, {"type": "function_call", "name": "semantic_search_wikipedia", "arguments": "{\"query\":\"Australian raven adaptation to urban environments behavior diet nesting cities human environments\"}", "call_id": "call_WbADgXS9IxEAESlBrigOyO4p", "id": "fc_0d44d690dddacab3006ab349df46a487d2b5923483e6f9dea3", "index": 1}]
-{"name": "semantic_search_wikipedia", "args": {"query": "Australian raven adaptation to urban environments behavior diet nesting cities human environments"}, "id": "call_WbADgXS9IxEAESlBrigOyO4p", "type": "tool_call"}</t>
+    <t>[{"id": "rs_00c74ffe835d510a006ab36d1b328c87d293fecbf0117c329d", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs20bT2kEVX6NQX6qb2L6SJzgWQLsi2sDBKGQI3E-MwzVSAm__OO4RHN_lP68j91Dr1cJRkkSE98C6bxr6YaDoqjLe44urJo_kPLCtUtj92ChxCu0R0QAOh5U7ipQu2u1PpImXL8NpfOa1MHMa_D2bdHZ1N8C0uowFAeVnLNmvbrO8okbde6JJA7OCmianOwRAjmp9w9O7OeKYvsfhg5G5CQ_3oTmdcdkPtV-TRaDZqilaMa6WVuqJvCVG8-V4ZSVV9sAeQMX4H_1yAPbWFLvJGfpZdY93ytW0rHj2J-FAuv33do_fl_P_FypNQwi3wUyyd8yMZKOeRQrswXyXogV6NoVfcf3C4leCYv3fTVsVPXhpv34ktfNdJWJbYgW92CioHWmN51OsfVp36U2HWE8tKQFtEFKIw-HJ79tux-cqQiGXiqybFIuRNBs9THVn3ZmDiq7oJjNym9LrpQnLLVZFSMW71ZMDTBmchF0GTFmtibx8Y0du1DdRIeNttmkfR9DeK1zoro-b3hEojA3gDx9L9eDpsEZs27v9UlkzdBZ_nU2SD5yHa4UfDuhn8t6Up654uWtQQBjqXQSKjZZ4X2KzQECqvsmOivij7kW5vgAovScnEYnXlGRq01fxAGwBSbrS6i-HBtn7iV9_OMOWgkHddKH2IjGHIZDQudXf4LFGmCjWTyO8lwnfo7MUTQaaEBE82cGh4h95_erw6oklJCyPc4sdPPnaUx_VlZ03yJCBVBEoc82kmF9x70Ii8MfaJR-1G7Jlz8kUFqLwPI-qRkQCcN73PDiaMHEqhd0wPsUBhpZr0HnapYTlXE0BJE4P8rObTcOIUS6wBqlSNzqFnJyHAJkB5EnAX4B7AGpqIb8C2hk9DvyW2qsNJpvjJ46zcRLJeFkoRbeqab-zDQyhPXmNEsxnCxdRaU10o2_9UyRpBo84uNzi9V5i9GtD29EsgTxh8HRTEPNP4_Rtw80Qwxj8zMctYEASIdSjN940Nt-4m5tb2z1SJkyKsTCVLLpo8AjQJqeSrISdoM9f9nFpvhmmnHLFTmtKqf0YZiJ4z3XDhlCBmpNAiNuzs-fJ19X6gmev0IEJT8usPFx2TDmbgBL2JPrnGekGBiNzZGN2gKO4WTu1i_IsW8dXGo4V6ywqAftmO4xJiuxe2P9KZYE2JjWcq4Shdl9x6zg5h0MY2OMGTDsmWjNe95TaEYUNw6L5KFbHE7K"}, {"type": "function_call", "name": "semantic_search_wikipedia", "arguments": "{\"query\":\"Australian raven adaptations to urban environments behavior diet nesting human settlements\"}", "call_id": "call_AQH4MJl0cJsNloVilbKLUOvy", "id": "fc_00c74ffe835d510a006ab36d1b759487d2867d24323dfce81a", "index": 1}]
+{"name": "semantic_search_wikipedia", "args": {"query": "Australian raven adaptations to urban environments behavior diet nesting human settlements"}, "id": "call_AQH4MJl0cJsNloVilbKLUOvy", "type": "tool_call"}</t>
   </si>
   <si>
     <t>Call total</t>
@@ -358,25 +358,25 @@
     <t>Tool · semantic_search_wikipedia</t>
   </si>
   <si>
-    <t>01a0cc58-91f9-7ab1-9367-f0ec3b1987ea</t>
+    <t>01a0cce2-3500-74c3-872b-438ccd8db4dc</t>
   </si>
   <si>
     <t xml:space="preserve">    Arguments</t>
   </si>
   <si>
-    <t>{'query': 'Australian raven adaptation to urban environments behavior diet nesting cities human environments'}</t>
+    <t>{'query': 'Australian raven adaptations to urban environments behavior diet nesting human settlements'}</t>
   </si>
   <si>
     <t xml:space="preserve">    Result</t>
   </si>
   <si>
-    <t>{"passages": [{"id": "passage-00016828", "text": "1827, its species name highlighting its similarity with the carrion crow ( c. corone ). two subspecies are recognised, which differ slightly in calls and are quite divergent genetically. the preferred habitat is open woodland and transitional zones. it has adapted well to urban environments and is a common city bird in sydney, canberra and perth. an omnivorous and opportunistic feeder, it eats a wide variety of plant and animal material, as well as food waste from urban areas. in eastern australia its range is strongly correlated with the presence of sheep, and it has been blamed for killing lambs. however, this is very rare, and the raven most often scavenges for afterbirth and stillborn animals as well as newborn lamb faeces. the australian raven is territorial, with pairs generally bonding for life. breeding takes place between july and september, with almost no variation across its range. the nest is a bowl @ - @ shaped structure of sticks sited high in a tree, or occasionally in a man @ - @ made structure such as a windmill or other building. = =", "title": "Australian raven", "source": "https://huggingface.co/datasets/Salesforce/wikitext/tree/b08601e04326c79dfdd32d625aee71d232d685c3/wikitext-103-raw-v1", "token_end": 408, "source_row": 49964, "token_start": 188, "license": "CC-BY-SA-3.0", "cosine_distance": 0.2746517062187195}, {"id": "passage-00016848", "text": "##worms are rarely eaten. australian ravens have been reported killing birds of such size as young galahs ( eolophus roseicapillus ) and starlings ( sturnus vulgaris ). most mammals are eaten as carrion, as many species are too large for the raven to kill, though young rabbits are a frequent prey item. australian ravens drink water frequently, up to ten times a day in hot weather. birds have been observed dunking pieces of meat in water before eating them, as well as doing the same with hard biscuits to make them soggy and soft. australian ravens are intelligent birds, and like many other corvids have innovative methods of seeking out food. foraging takes place in the early morning or late afternoon ; birds rest in the hotter part of the day. food is taken mainly from the ground, birds either finding objects while flying overhead, or by walking along and looking. however, they occasionally feed in trees \u2014 australian ravens forage eucalypt foliage for christmas beetles ( anoplognathus ), and devote a substantial amount of time to look", "source_row": 49964, "license": "CC-BY-SA-3.0", "source": "https://huggingface.co/datasets/Salesforce/wikitext/tree/b08601e04326c79dfdd32d625aee71d232d685c3/wikitext-103-raw-v1", "token_start": 3948, "title": "Australian raven", "token_end": 4168, "cosine_distance": 0.3348250985145569}, {"id": "passage-00016845", "text": "distinguishing australian corvids has hampered understanding of seasonal movements. the australian raven is thought to be largely sedentary, with most movement of over 16 km ( 9 @. @ 9 mi ) due to flocks of non @ - @ breeding subadult birds. juvenile birds leave their parents and join flocks when they are four or five months old. smaller flocks of 8 \u2013 30 birds stay within an area of around 260 square kilometres, while larger flocks of up to 300 birds may travel hundreds of kilometres seeking food. a single breeding pair and their brood can occupy a territory of up to around 120 hectares ( 300 acres ) and remains there year @ - @ round, though groups of ravens may enter this area to forage. australian ravens will defend their territory by chasing, dive @ - @ bombing and occasionally striking the backs of birds of prey, foxes or even people. they generally mate for life, though occasionally one male has been found to be mated with two females in adjacent territories. if the female dies, the male australian raven maintains the territory and finds another mate, while", "source_row": 49964, "token_start": 3384, "title": "Australian raven", "token_end": 3604, "source": "https://huggingface.co/datasets/Salesforce/wikitext/tree/b08601e04326c79dfdd32d625aee71d232d685c3/wikitext-103-raw-v1", "license": "CC-BY-SA-3.0", "cosine_distance": 0.33717983961105347}, {"id": "passage-00016847", "text": "neck. this takes place particularly in autumn, winter and spring, and is important in pair bonding. either member may initiate it, generally by landing near the other bird, shuffling next to its mate, then bending its head forward and presenting its nape. = = = feeding = = = the australian raven is omnivorous, though eats more meat than smaller corvids. its diet in summer contains a high proportion of insects, while more plant items are eaten in autumn. flesh makes up over half its diet in winter. invertebrates commonly eaten include spiders, millipedes, centipedes ( which ravens behead before eating ), grasshoppers, cicadas and caterpillars ( especially of the family noctuidae ), which are important in feeding nestlings. australian ravens sometimes eat yabbies ( cherax destructor ) from the edges of dams. unusually for a ground @ - @ feeding omnivore, earthworms are rarely eaten. australian ravens have been reported killing birds of such size as young galahs ( eolophus roseicapillus ) and starlings", "license": "CC-BY-SA-3.0", "token_end": 3980, "title": "Australian raven", "source_row": 49964, "source": "https://huggingface.co/datasets/Salesforce/wikitext/tree/b08601e04326c79dfdd32d625aee71d232d685c3/wikitext-103-raw-v1", "token_start": 3760, "cosine_distance": 0.345275342464447}], "note": "Nearest passages are candidates, not proof of relevance; abstain if they do not answer the question."}</t>
+    <t>{"passages": [{"id": "passage-00016828", "text": "1827, its species name highlighting its similarity with the carrion crow ( c. corone ). two subspecies are recognised, which differ slightly in calls and are quite divergent genetically. the preferred habitat is open woodland and transitional zones. it has adapted well to urban environments and is a common city bird in sydney, canberra and perth. an omnivorous and opportunistic feeder, it eats a wide variety of plant and animal material, as well as food waste from urban areas. in eastern australia its range is strongly correlated with the presence of sheep, and it has been blamed for killing lambs. however, this is very rare, and the raven most often scavenges for afterbirth and stillborn animals as well as newborn lamb faeces. the australian raven is territorial, with pairs generally bonding for life. breeding takes place between july and september, with almost no variation across its range. the nest is a bowl @ - @ shaped structure of sticks sited high in a tree, or occasionally in a man @ - @ made structure such as a windmill or other building. = =", "license": "CC-BY-SA-3.0", "source_row": 49964, "token_start": 188, "title": "Australian raven", "token_end": 408, "source": "https://huggingface.co/datasets/Salesforce/wikitext/tree/b08601e04326c79dfdd32d625aee71d232d685c3/wikitext-103-raw-v1", "cosine_distance": 0.2472367286682129}, {"id": "passage-00016848", "text": "##worms are rarely eaten. australian ravens have been reported killing birds of such size as young galahs ( eolophus roseicapillus ) and starlings ( sturnus vulgaris ). most mammals are eaten as carrion, as many species are too large for the raven to kill, though young rabbits are a frequent prey item. australian ravens drink water frequently, up to ten times a day in hot weather. birds have been observed dunking pieces of meat in water before eating them, as well as doing the same with hard biscuits to make them soggy and soft. australian ravens are intelligent birds, and like many other corvids have innovative methods of seeking out food. foraging takes place in the early morning or late afternoon ; birds rest in the hotter part of the day. food is taken mainly from the ground, birds either finding objects while flying overhead, or by walking along and looking. however, they occasionally feed in trees \u2014 australian ravens forage eucalypt foliage for christmas beetles ( anoplognathus ), and devote a substantial amount of time to look", "token_start": 3948, "title": "Australian raven", "source_row": 49964, "token_end": 4168, "source": "https://huggingface.co/datasets/Salesforce/wikitext/tree/b08601e04326c79dfdd32d625aee71d232d685c3/wikitext-103-raw-v1", "license": "CC-BY-SA-3.0", "cosine_distance": 0.30797886848449707}, {"id": "passage-00016845", "text": "distinguishing australian corvids has hampered understanding of seasonal movements. the australian raven is thought to be largely sedentary, with most movement of over 16 km ( 9 @. @ 9 mi ) due to flocks of non @ - @ breeding subadult birds. juvenile birds leave their parents and join flocks when they are four or five months old. smaller flocks of 8 \u2013 30 birds stay within an area of around 260 square kilometres, while larger flocks of up to 300 birds may travel hundreds of kilometres seeking food. a single breeding pair and their brood can occupy a territory of up to around 120 hectares ( 300 acres ) and remains there year @ - @ round, though groups of ravens may enter this area to forage. australian ravens will defend their territory by chasing, dive @ - @ bombing and occasionally striking the backs of birds of prey, foxes or even people. they generally mate for life, though occasionally one male has been found to be mated with two females in adjacent territories. if the female dies, the male australian raven maintains the territory and finds another mate, while", "token_start": 3384, "source": "https://huggingface.co/datasets/Salesforce/wikitext/tree/b08601e04326c79dfdd32d625aee71d232d685c3/wikitext-103-raw-v1", "title": "Australian raven", "token_end": 3604, "license": "CC-BY-SA-3.0", "source_row": 49964, "cosine_distance": 0.3088942766189575}, {"id": "passage-00016847", "text": "neck. this takes place particularly in autumn, winter and spring, and is important in pair bonding. either member may initiate it, generally by landing near the other bird, shuffling next to its mate, then bending its head forward and presenting its nape. = = = feeding = = = the australian raven is omnivorous, though eats more meat than smaller corvids. its diet in summer contains a high proportion of insects, while more plant items are eaten in autumn. flesh makes up over half its diet in winter. invertebrates commonly eaten include spiders, millipedes, centipedes ( which ravens behead before eating ), grasshoppers, cicadas and caterpillars ( especially of the family noctuidae ), which are important in feeding nestlings. australian ravens sometimes eat yabbies ( cherax destructor ) from the edges of dams. unusually for a ground @ - @ feeding omnivore, earthworms are rarely eaten. australian ravens have been reported killing birds of such size as young galahs ( eolophus roseicapillus ) and starlings", "title": "Australian raven", "token_start": 3760, "token_end": 3980, "source_row": 49964, "source": "https://huggingface.co/datasets/Salesforce/wikitext/tree/b08601e04326c79dfdd32d625aee71d232d685c3/wikitext-103-raw-v1", "license": "CC-BY-SA-3.0", "cosine_distance": 0.31524449586868286}], "note": "Nearest passages are candidates, not proof of relevance; abstain if they do not answer the question."}</t>
   </si>
   <si>
     <t>R2</t>
   </si>
   <si>
-    <t>01a0cc58-9315-7f03-abbd-5ad6b6f55d69</t>
+    <t>01a0cce2-361c-7c92-a6e3-3f28349a5186</t>
   </si>
   <si>
     <t>Conversation history · cache read</t>
@@ -385,7 +385,7 @@
     <t xml:space="preserve">    Tool result</t>
   </si>
   <si>
-    <t>[{"id": "rs_0d44d690dddacab3006ab349e0a53887d289c20a9a61c86c6d", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs0nhI8a24ZsyVY_fZp9npmhVIsvo-Rx4AWS7ZmP5wQZwBmqlN1RYqXwTYBhA0gYATVqzTj-YfLDLWvPZTgJ40FspIEoM1ZB8_JjA31_4cFwb58jA9c0WB9nHR5dD-lxEhMn7sK6nDKnouonhf-ujFKDejSY1c2eElAJD4upfC-N1b5uaCDIo3u5KSjkXM-IMVWrCwE1R0U4wZ9krh87M0QHd_MXBpiM83AEqtUcn2wOyJBuQafxr33uqJnGqS_cWT7iFdh8fejuooFCMigkOJIMjkpI68EN0o_bDxc4KrNu98aIKJf9kyYe9zpMcWJyYnPOsD3gyjo47yECYgP8xnLOwwN7gLmo2o5TYXuSzGtVyER5WJEFXCyyvnrhEaUKmZftQHIvJ5nFHXDMb5i2PZg45ccICWbP-M8ALN4LdScbdbkLWawQI3BK3koKmH4nMUszc3aa16nfNNO5U-naaYYbWEgU488SWjFV-ksljEDhv6Fj2Rpma8SfTA_c9706xAWNBfimfitR7QF82BWZj2ktEyKjE8SynteGrTewQalY76_xjs8c9K7LlLJbJSYxqRFUElfcswxjo8U9-j4361g3wgQkZJz7VOM1b3SNCuAryGhwjQSma5UG14wqgrE6FhP_2BmWXkP0wnrUcp6gZheX3KwjV5qtS00by17gAli9cBC30IlYseoRH5QCEnGCtUSY4c6eXKGIDDBPcUWmcjeDlWZbALNs9h4imqeK9V5Ah0Dh-s6of9VMj5uzXZf280jYo-TAt-lhoDKulVS3UYHtLQ0OIqEeblHvKX3UsFjrBI4N6CEwZO0GNvweDQxMvtbmC2ocAxYtsBrocKs2heE3bcfDTsJDOoF6sXAuPEO_cDQe0gNJH_drOCo2N9gO9_nmFz_VRtrt_ayiz7HdXRZSysHlt6816W49nYlTa_S48zU2rwTMuGQprI_iMJ4EC8oNeWBx5u69BygFRqJhKVUKm2pDGLXWCdo-cVITqZqZt0ocXTDsudezcRz9sCoSO1q8uuuNceTMf2tI7630Gz01ubvcTeW0y0HGtlJRuradTEiw-E2omfFal7hpdmOzOQGYd-f6zEIuY6eNFkDAUGBr1aE7pa68cklypzHMCdXaorFrmb2HYET0f_suEdhK5B47nBVpXEWAxljDwbXjP7zwkvgTDEMQBXyOR1tAjEoW28jKVjkq3e3P7T0pdlWqgF_tpZplz8YYjoQ7HaTij0N8JjR619H0W8JAwHaOMO5ecLreafyC1YVKr1E2IcbQXPyBLHTIh2nQ17HpBLs-jSWTnYNkTZX8noKm_trdFGfa_tdrUJq1U4nOORjiQAO1MgWUBcocTsrlTXBh8J9FVa6Ts4JOhlcBnlCNSfqjNcAN8zlMSmhS7XsvzczQkn3-qHDUf-W8kGEE7rEYnNp5I6g_T2mCYIzkdTIWDeKbNvZjDaJ9IsMSg1rHJqICqXBKp7rZJ9j16l6trq6SuaYhKWKnKskJwHAByY83lkufXYdsm7DQ="}, {"type": "text", "text": "The Australian raven has adapted to urban environments by:\n\n- **Exploiting abundant food:** It is an opportunistic omnivore and consumes food waste in urban areas, alongside a wide range of plant and animal matter [passage-00016828].\n- **Using built structures for nesting:** Although it usually nests high in trees, it sometimes builds nests on human-made structures such as windmills and buildings [passage-00016828].\n- **Living successfully in cities:** It is described as common and well adapted to urban areas, including Sydney, Canberra, and Perth [passage-00016828].\n\nThe indexed evidence does not provide much detail on other possible urban adaptations, such as changes in calls, traffic avoidance, or altered breeding behavior.", "phase": "final_answer", "index": 1, "id": "msg_0d44d690dddacab3006ab349e1367487d28af360b4f4ef8fdb"}]</t>
+    <t>[{"id": "rs_00c74ffe835d510a006ab36d1cdd6c87d2b7c8ab0baff2fdba", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs20dAkpGdjLgTzLVBsV2VsFlNNBHMOdswyMgBCh2bQ3eQ3KBVeTuOb-K94sjVLNTQuMlpI--TCaHt6fj2ERM-fG0ag7Zn8AfEbbRyD2i29tv1-CgJT655SQdnb6MRrpxcqN9jBpQ6ufKCGlPiULHIrwLBMvbnPYUtemD4Jwb6zbgnLvQtAJiU8RGM458xYdyrnnowyZrs6RIbwGwigQS6CpW33kJ_tX6VQAk6COrjF6a7hIGpTx682c92nILYGRxmwMhZ4TEUZwc4ov5wiQ7jAsiw_k4jgLTw5VayfzN4IAAQAjd4RPbEd_W0T86-nRml1Z0Z_9V7grexesmNSpNjFHl3pnqdivcxjE36rknuWfDrCW7hLBGNrpjvW-OYx34MdXGKpPdeEkcW6Cq2ZMmGWRbsowfAj-aBJ6AZ1Tl9oM6gMWgawGBdabAsPz5BSi-PBDyoi_7UAwbYH_zb_cwHIRhLvP_Fj8lgBZnPOl1odIHCx3kohEClqXxgR7CKUSEtDp85K41pUst6tET0atKtwnDSuVL2hS8clcJ_Q7RTcVMmzOsU6CEXno66sYJ_XuHXfysewMmVRkJDkWySPZi2lVTa8eUPy9RHJtQrtiyQ9LhoOsQ1YGxzez8TcxMvSQweRcuaW9lfZjWm-0wUa6Z7gWuADdDTl75ScTVJJvT_W9wXn1BCgdQlbqt-7MU_Flhj_RrYi9OdUz4FEmKISfN35xt1H8EL-oQzKt7XWN6XnOru73DPCJz9i_9HngXFjA-ljWv7LhF3N7FkULoSqY9LGrfaHqRMx1jkJZVQJgcZd9Ksq9SDH-K-g0-g4msEyCyRJVtY5yF3Gso66MjfqwCw__GdaKXnZhVsll92fudcHEqN66HDpzDR5pEt4sNzq2wWgtyxmchn_07M0AFMqN24r4ZpoL9CrMnXw0UgJIEKAACfmilcljTeZKlPupBoX0RdJs4pKhsCiMezb-nmv7FuXkL5dui8605teZtgHPeS3kBREw9lb67RfyRL0Zfu4XuBIU0LY65EIJ8w5XFg6Y2RVq_2ruagLiyaRGFVCd64aTvxgJCQulzN_zHSKReKTiCyzIko9wUwumcIE8ksR1Fo5AxudHSmZaspWB-AP0wqtbLju6E3uNBtD4vES-uDlzYxxqfl-woNcOMSkisxpx7CPhOCilYRjeB-gasXtNjrabpCMPf-pyBv3eSdzksyi-yqsLtJy0dG0lzGOG5IuFjT6D-ZWibB6cFnJhI68XBuyvb3KP_y5T5Vt3zURF4dvTbHILtyIDjtsj5ZFUiaEhSfHg8LISX105NENLkxZaAGNRk6pI-LQB3I0eLTCmu4xRCtJy7btd5jQjjTIMEAGRsWKWt5ZOnMVI2ZgJV5OeoFaOVE0KksoBvTuPJ048390i7zZIfufpCminCnpCTOFrQrSwdL_yYf7VcX4s0MMqYaHsIgkc8oQwSAvKDi7lNYdri8ljd1fdT-29l9NV_Ra1QnKSDivWevkpXPSAZ22oyt1IfxeNgRLvZ8ZeNbCkPBNyYyNilwk_nlfi6ak4SM3XuH1P4Kg=="}, {"type": "text", "text": "The Australian raven has adapted to cities in several ways:\n\n- **Flexible diet:** It is an omnivorous, opportunistic feeder and readily scavenges **food waste** in urban areas. [passage-00016828]\n- **Use of built structures:** Although it usually nests high in trees, it can also nest on **man-made structures**, including windmills and buildings. [passage-00016828]\n- **Tolerance of urban living:** These adaptations have enabled it to become a **common city bird** in Sydney, Canberra, and Perth. [passage-00016828]\n\nThe indexed evidence supports these points, but does not provide much detail on other possible urban adaptations, such as changes in nesting timing or responses to traffic and human disturbance.", "phase": "final_answer", "index": 1, "id": "msg_00c74ffe835d510a006ab36d1d895487d2ae5930ead501cf96"}]</t>
   </si>
   <si>
     <t>wikipedia_rag_agent</t>
@@ -406,7 +406,7 @@
     <t>Prepare the current conversation, run model middleware, and invoke the chat model.</t>
   </si>
   <si>
-    <t>01a0cc58-8c60-7c60-b102-1be5d5c5e8d3</t>
+    <t>01a0cce2-2de6-7af2-81fa-f7556940a1e3</t>
   </si>
   <si>
     <t xml:space="preserve">        ChatOpenAI</t>
@@ -427,7 +427,7 @@
     <t>Execute tool calls requested by the preceding model response and return their observations.</t>
   </si>
   <si>
-    <t>01a0cc58-91f8-75f3-a9ca-36eda6d8220b</t>
+    <t>01a0cce2-34ff-7452-bcb0-c562b10c3022</t>
   </si>
   <si>
     <t>No model charge</t>
@@ -443,7 +443,7 @@
 passages are candidates; check relevance before using them as evidence.</t>
   </si>
   <si>
-    <t>01a0cc58-9315-7f03-abbd-5acadfba3503</t>
+    <t>01a0cce2-361b-79c2-a53f-02049fba08f5</t>
   </si>
 </sst>
 </file>
@@ -911,19 +911,19 @@
       </c>
       <c r="E2" s="2">
         <f>IF(COUNT('Turns'!E17,'Turns'!E33)=2,SUM('Turns'!E17,'Turns'!E33),"Unknown")</f>
-        <v>0.000654015789</v>
+        <v>0.000668671605</v>
       </c>
       <c r="F2" s="2">
         <f>IF(COUNT('Turns'!F17,'Turns'!F33)=2,SUM('Turns'!F17,'Turns'!F33),"Unknown")</f>
-        <v>0.0007497</v>
+        <v>0.0007665</v>
       </c>
       <c r="G2" s="5">
         <f>IF(ISNUMBER(E2),ROUND(E2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>65.0</v>
+        <v>67.0</v>
       </c>
       <c r="H2" s="5">
         <f>IF(ISNUMBER(F2),ROUND(F2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>75.0</v>
+        <v>77.0</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -935,19 +935,19 @@
       </c>
       <c r="E3" s="2">
         <f>IF(COUNT('Turns'!E17,'Turns'!E33)=2,SUM('Turns'!E17,'Turns'!E33),"Unknown")</f>
-        <v>0.000654015789</v>
+        <v>0.000668671605</v>
       </c>
       <c r="F3" s="2">
         <f>IF(COUNT('Turns'!F17,'Turns'!F33)=2,SUM('Turns'!F17,'Turns'!F33),"Unknown")</f>
-        <v>0.0007497</v>
+        <v>0.0007665</v>
       </c>
       <c r="G3" s="5">
         <f>IF(ISNUMBER(E3),ROUND(E3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>65.0</v>
+        <v>67.0</v>
       </c>
       <c r="H3" s="5">
         <f>IF(ISNUMBER(F3),ROUND(F3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>75.0</v>
+        <v>77.0</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -1072,7 +1072,7 @@
         <v>105</v>
       </c>
       <c r="D11" s="4">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="24" customHeight="1">
@@ -1116,15 +1116,15 @@
         <v>107</v>
       </c>
       <c r="D13" s="5">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E13" s="2">
         <f>IF(AND(ISNUMBER(F13),ISNUMBER('Reference data'!$B$3)),F13*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.4545852e-05</v>
+        <v>3.3499008e-05</v>
       </c>
       <c r="F13" s="2">
         <f>IF(D13=0,0,IF(ISNUMBER('Reference data'!E17),D13*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>3.96e-05</v>
+        <v>3.84e-05</v>
       </c>
       <c r="G13" s="5">
         <f>IF(ISNUMBER(E13),ROUND(E13*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1183,11 +1183,11 @@
       </c>
       <c r="E17" s="2">
         <f>IF(COUNT('Turns'!E5,'Turns'!E12,'Turns'!E13)=3,SUM('Turns'!E5,'Turns'!E12,'Turns'!E13),"Unknown")</f>
-        <v>7.6943034e-05</v>
+        <v>7.589619e-05</v>
       </c>
       <c r="F17" s="2">
         <f>IF(COUNT('Turns'!F5,'Turns'!F12,'Turns'!F13)=3,SUM('Turns'!F5,'Turns'!F12,'Turns'!F13),"Unknown")</f>
-        <v>8.82e-05</v>
+        <v>8.7e-05</v>
       </c>
       <c r="G17" s="5">
         <f>IF(ISNUMBER(E17),ROUND(E17*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1383,7 +1383,7 @@
         <v>105</v>
       </c>
       <c r="D27" s="4">
-        <v>202</v>
+        <v>217</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="24" customHeight="1">
@@ -1397,23 +1397,23 @@
         <v>106</v>
       </c>
       <c r="D28" s="5">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="E28" s="2">
         <f>IF(AND(ISNUMBER(F28),ISNUMBER('Reference data'!$B$3)),F28*'Reference data'!$B$3,"Unknown")</f>
-        <v>4.8154824e-05</v>
+        <v>5.9670108e-05</v>
       </c>
       <c r="F28" s="2">
         <f>IF(D28=0,0,IF(ISNUMBER('Reference data'!F17),D28*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>5.52e-05</v>
+        <v>6.84e-05</v>
       </c>
       <c r="G28" s="5">
         <f>IF(ISNUMBER(E28),ROUND(E28*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="H28" s="5">
         <f>IF(ISNUMBER(F28),ROUND(F28*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="24" customHeight="1">
@@ -1427,19 +1427,19 @@
         <v>107</v>
       </c>
       <c r="D29" s="5">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E29" s="2">
         <f>IF(AND(ISNUMBER(F29),ISNUMBER('Reference data'!$B$3)),F29*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.000163307664</v>
+        <v>0.00016749504</v>
       </c>
       <c r="F29" s="2">
         <f>IF(D29=0,0,IF(ISNUMBER('Reference data'!E17),D29*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>0.0001872</v>
+        <v>0.000192</v>
       </c>
       <c r="G29" s="5">
         <f>IF(ISNUMBER(E29),ROUND(E29*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="H29" s="5">
         <f>IF(ISNUMBER(F29),ROUND(F29*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1494,19 +1494,19 @@
       </c>
       <c r="E33" s="2">
         <f>IF(COUNT('Turns'!E22,'Turns'!E23,'Turns'!E25,'Turns'!E28,'Turns'!E29)=5,SUM('Turns'!E22,'Turns'!E23,'Turns'!E25,'Turns'!E28,'Turns'!E29),"Unknown")</f>
-        <v>0.000577072755</v>
+        <v>0.000592775415</v>
       </c>
       <c r="F33" s="2">
         <f>IF(COUNT('Turns'!F22,'Turns'!F23,'Turns'!F25,'Turns'!F28,'Turns'!F29)=5,SUM('Turns'!F22,'Turns'!F23,'Turns'!F25,'Turns'!F28,'Turns'!F29),"Unknown")</f>
-        <v>0.0006615</v>
+        <v>0.0006795</v>
       </c>
       <c r="G33" s="5">
         <f>IF(ISNUMBER(E33),ROUND(E33*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>58.0</v>
+        <v>59.0</v>
       </c>
       <c r="H33" s="5">
         <f>IF(ISNUMBER(F33),ROUND(F33*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>66.0</v>
+        <v>68.0</v>
       </c>
       <c r="K33" s="4" t="s">
         <v>111</v>
@@ -1692,46 +1692,46 @@
       </c>
       <c r="S2" s="2">
         <f>IF(COUNT('Turns'!D13,'Turns'!D29)=2,SUM('Turns'!D13,'Turns'!D29),"Unknown")</f>
-        <v>189.0</v>
+        <v>192.0</v>
       </c>
       <c r="T2" s="2">
         <f>IF(COUNT('Turns'!E13,'Turns'!E29)=2,SUM('Turns'!E13,'Turns'!E29),"Unknown")</f>
-        <v>0.000197853516</v>
+        <v>0.000200994048</v>
       </c>
       <c r="U2" s="2">
         <f>IF(COUNT('Turns'!F13,'Turns'!F29)=2,SUM('Turns'!F13,'Turns'!F29),"Unknown")</f>
-        <v>0.0002268</v>
+        <v>0.0002304</v>
       </c>
       <c r="V2" s="2">
         <f>IF(COUNT('Turns'!D12,'Turns'!D28)=2,SUM('Turns'!D12,'Turns'!D28),"Unknown")</f>
-        <v>55.0</v>
+        <v>66.0</v>
       </c>
       <c r="W2" s="2">
         <f>IF(COUNT('Turns'!E12,'Turns'!E28)=2,SUM('Turns'!E12,'Turns'!E28),"Unknown")</f>
-        <v>5.757642e-05</v>
+        <v>6.9091704e-05</v>
       </c>
       <c r="X2" s="2">
         <f>IF(COUNT('Turns'!F12,'Turns'!F28)=2,SUM('Turns'!F12,'Turns'!F28),"Unknown")</f>
-        <v>6.6e-05</v>
+        <v>7.92e-05</v>
       </c>
       <c r="Y2" s="2">
         <f>IF(COUNT('Turns'!E17,'Turns'!E33)=2,SUM('Turns'!E17,'Turns'!E33),"Unknown")</f>
-        <v>0.000654015789</v>
+        <v>0.000668671605</v>
       </c>
       <c r="Z2" s="2">
         <f>IF(COUNT('Turns'!F17,'Turns'!F33)=2,SUM('Turns'!F17,'Turns'!F33),"Unknown")</f>
-        <v>0.0007497</v>
+        <v>0.0007665</v>
       </c>
       <c r="AA2" s="5">
         <f>IF(ISNUMBER(Y2),ROUND(Y2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>65.0</v>
+        <v>67.0</v>
       </c>
       <c r="AB2" s="5">
         <f>IF(ISNUMBER(Z2),ROUND(Z2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>75.0</v>
+        <v>77.0</v>
       </c>
       <c r="AD2" s="1">
-        <v>4808.696</v>
+        <v>4821.405</v>
       </c>
       <c r="AE2" s="1" t="s">
         <v>126</v>
@@ -1794,15 +1794,15 @@
       </c>
       <c r="S3" s="2">
         <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
-        <v>33.0</v>
+        <v>32.0</v>
       </c>
       <c r="T3" s="2">
         <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>3.4545852e-05</v>
+        <v>3.3499008e-05</v>
       </c>
       <c r="U3" s="2">
         <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
-        <v>3.96e-05</v>
+        <v>3.84e-05</v>
       </c>
       <c r="V3" s="2">
         <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
@@ -1818,11 +1818,11 @@
       </c>
       <c r="Y3" s="2">
         <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>7.6943034e-05</v>
+        <v>7.589619e-05</v>
       </c>
       <c r="Z3" s="2">
         <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>8.82e-05</v>
+        <v>8.7e-05</v>
       </c>
       <c r="AA3" s="5">
         <f>IF(ISNUMBER(Y3),ROUND(Y3*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1833,7 +1833,7 @@
         <v>9.0</v>
       </c>
       <c r="AD3" s="1">
-        <v>1430.845</v>
+        <v>1816.119</v>
       </c>
       <c r="AE3" s="1" t="s">
         <v>126</v>
@@ -1899,15 +1899,15 @@
       </c>
       <c r="S4" s="2">
         <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
-        <v>33.0</v>
+        <v>32.0</v>
       </c>
       <c r="T4" s="2">
         <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>3.4545852e-05</v>
+        <v>3.3499008e-05</v>
       </c>
       <c r="U4" s="2">
         <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
-        <v>3.96e-05</v>
+        <v>3.84e-05</v>
       </c>
       <c r="V4" s="2">
         <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
@@ -1923,11 +1923,11 @@
       </c>
       <c r="Y4" s="2">
         <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>7.6943034e-05</v>
+        <v>7.589619e-05</v>
       </c>
       <c r="Z4" s="2">
         <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>8.82e-05</v>
+        <v>8.7e-05</v>
       </c>
       <c r="AA4" s="5">
         <f>IF(ISNUMBER(Y4),ROUND(Y4*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1941,7 +1941,7 @@
         <v>93</v>
       </c>
       <c r="AD4" s="1">
-        <v>1428.307</v>
+        <v>1813.714</v>
       </c>
       <c r="AE4" s="1" t="s">
         <v>133</v>
@@ -1973,7 +1973,7 @@
         <v>49</v>
       </c>
       <c r="AD5" s="1">
-        <v>283.813</v>
+        <v>282.83</v>
       </c>
       <c r="AE5" s="1" t="s">
         <v>137</v>
@@ -2005,7 +2005,7 @@
         <v>136</v>
       </c>
       <c r="AD6" s="1">
-        <v>281.92</v>
+        <v>280.309</v>
       </c>
       <c r="AE6" s="1" t="s">
         <v>137</v>
@@ -2074,46 +2074,46 @@
       </c>
       <c r="S7" s="2">
         <f>IF(COUNT('Turns'!D29)=1,SUM('Turns'!D29),"Unknown")</f>
-        <v>156.0</v>
+        <v>160.0</v>
       </c>
       <c r="T7" s="2">
         <f>IF(COUNT('Turns'!E29)=1,SUM('Turns'!E29),"Unknown")</f>
-        <v>0.000163307664</v>
+        <v>0.00016749504</v>
       </c>
       <c r="U7" s="2">
         <f>IF(COUNT('Turns'!F29)=1,SUM('Turns'!F29),"Unknown")</f>
-        <v>0.0001872</v>
+        <v>0.000192</v>
       </c>
       <c r="V7" s="2">
         <f>IF(COUNT('Turns'!D28)=1,SUM('Turns'!D28),"Unknown")</f>
-        <v>46.0</v>
+        <v>57.0</v>
       </c>
       <c r="W7" s="2">
         <f>IF(COUNT('Turns'!E28)=1,SUM('Turns'!E28),"Unknown")</f>
-        <v>4.8154824e-05</v>
+        <v>5.9670108e-05</v>
       </c>
       <c r="X7" s="2">
         <f>IF(COUNT('Turns'!F28)=1,SUM('Turns'!F28),"Unknown")</f>
-        <v>5.52e-05</v>
+        <v>6.84e-05</v>
       </c>
       <c r="Y7" s="2">
         <f>IF(COUNT('Turns'!E33)=1,SUM('Turns'!E33),"Unknown")</f>
-        <v>0.000577072755</v>
+        <v>0.000592775415</v>
       </c>
       <c r="Z7" s="2">
         <f>IF(COUNT('Turns'!F33)=1,SUM('Turns'!F33),"Unknown")</f>
-        <v>0.0006615</v>
+        <v>0.0006795</v>
       </c>
       <c r="AA7" s="5">
         <f>IF(ISNUMBER(Y7),ROUND(Y7*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>58.0</v>
+        <v>59.0</v>
       </c>
       <c r="AB7" s="5">
         <f>IF(ISNUMBER(Z7),ROUND(Z7*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>66.0</v>
+        <v>68.0</v>
       </c>
       <c r="AD7" s="1">
-        <v>3087.908</v>
+        <v>2717.693</v>
       </c>
       <c r="AE7" s="1" t="s">
         <v>126</v>
@@ -2185,49 +2185,49 @@
       </c>
       <c r="S8" s="2">
         <f>IF(COUNT('Turns'!D29)=1,SUM('Turns'!D29),"Unknown")</f>
-        <v>156.0</v>
+        <v>160.0</v>
       </c>
       <c r="T8" s="2">
         <f>IF(COUNT('Turns'!E29)=1,SUM('Turns'!E29),"Unknown")</f>
-        <v>0.000163307664</v>
+        <v>0.00016749504</v>
       </c>
       <c r="U8" s="2">
         <f>IF(COUNT('Turns'!F29)=1,SUM('Turns'!F29),"Unknown")</f>
-        <v>0.0001872</v>
+        <v>0.000192</v>
       </c>
       <c r="V8" s="2">
         <f>IF(COUNT('Turns'!D28)=1,SUM('Turns'!D28),"Unknown")</f>
-        <v>46.0</v>
+        <v>57.0</v>
       </c>
       <c r="W8" s="2">
         <f>IF(COUNT('Turns'!E28)=1,SUM('Turns'!E28),"Unknown")</f>
-        <v>4.8154824e-05</v>
+        <v>5.9670108e-05</v>
       </c>
       <c r="X8" s="2">
         <f>IF(COUNT('Turns'!F28)=1,SUM('Turns'!F28),"Unknown")</f>
-        <v>5.52e-05</v>
+        <v>6.84e-05</v>
       </c>
       <c r="Y8" s="2">
         <f>IF(COUNT('Turns'!E33)=1,SUM('Turns'!E33),"Unknown")</f>
-        <v>0.000577072755</v>
+        <v>0.000592775415</v>
       </c>
       <c r="Z8" s="2">
         <f>IF(COUNT('Turns'!F33)=1,SUM('Turns'!F33),"Unknown")</f>
-        <v>0.0006615</v>
+        <v>0.0006795</v>
       </c>
       <c r="AA8" s="5">
         <f>IF(ISNUMBER(Y8),ROUND(Y8*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>58.0</v>
+        <v>59.0</v>
       </c>
       <c r="AB8" s="5">
         <f>IF(ISNUMBER(Z8),ROUND(Z8*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>66.0</v>
+        <v>68.0</v>
       </c>
       <c r="AC8" s="1" t="s">
         <v>118</v>
       </c>
       <c r="AD8" s="1">
-        <v>3085.068</v>
+        <v>2715.842</v>
       </c>
       <c r="AE8" s="1" t="s">
         <v>133</v>

--- a/reports/rag_chat/report.xlsx
+++ b/reports/rag_chat/report.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="142">
   <si>
     <t>Request</t>
   </si>
@@ -75,13 +75,13 @@
     <t>Parent ID</t>
   </si>
   <si>
-    <t>Fresh input tokens</t>
-  </si>
-  <si>
-    <t>Fresh input EUR</t>
-  </si>
-  <si>
-    <t>Fresh input USD</t>
+    <t>Input at standard rate tokens</t>
+  </si>
+  <si>
+    <t>Input at standard rate EUR</t>
+  </si>
+  <si>
+    <t>Input at standard rate USD</t>
   </si>
   <si>
     <t>Cache read tokens</t>
@@ -165,7 +165,7 @@
     <t>Run ID</t>
   </si>
   <si>
-    <t>01a0cce2-2de3-71b1-a3b6-5767197c0214</t>
+    <t>01a0d134-365e-7531-a1be-bfe2a5d9498f</t>
   </si>
   <si>
     <t>Recording</t>
@@ -177,13 +177,13 @@
     <t>FX reference date</t>
   </si>
   <si>
-    <t>2026-09-22</t>
+    <t>2026-09-23</t>
   </si>
   <si>
     <t>FX fetched at</t>
   </si>
   <si>
-    <t>2026-09-23T06:06:28.037095Z</t>
+    <t>2026-09-24T02:09:35.117183Z</t>
   </si>
   <si>
     <t>UTC</t>
@@ -306,10 +306,10 @@
     <t>gpt-5.6-luna</t>
   </si>
   <si>
-    <t>01a0cce2-2de7-7012-bcd4-719bc907d99e</t>
-  </si>
-  <si>
-    <t>Fresh input</t>
+    <t>01a0d134-3663-7130-a324-ff0cb990ac3b</t>
+  </si>
+  <si>
+    <t>Input at standard rate</t>
   </si>
   <si>
     <t xml:space="preserve">    Tool definitions</t>
@@ -345,8 +345,8 @@
     <t xml:space="preserve">    Output content</t>
   </si>
   <si>
-    <t>[{"id": "rs_00c74ffe835d510a006ab36d1b328c87d293fecbf0117c329d", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs20bT2kEVX6NQX6qb2L6SJzgWQLsi2sDBKGQI3E-MwzVSAm__OO4RHN_lP68j91Dr1cJRkkSE98C6bxr6YaDoqjLe44urJo_kPLCtUtj92ChxCu0R0QAOh5U7ipQu2u1PpImXL8NpfOa1MHMa_D2bdHZ1N8C0uowFAeVnLNmvbrO8okbde6JJA7OCmianOwRAjmp9w9O7OeKYvsfhg5G5CQ_3oTmdcdkPtV-TRaDZqilaMa6WVuqJvCVG8-V4ZSVV9sAeQMX4H_1yAPbWFLvJGfpZdY93ytW0rHj2J-FAuv33do_fl_P_FypNQwi3wUyyd8yMZKOeRQrswXyXogV6NoVfcf3C4leCYv3fTVsVPXhpv34ktfNdJWJbYgW92CioHWmN51OsfVp36U2HWE8tKQFtEFKIw-HJ79tux-cqQiGXiqybFIuRNBs9THVn3ZmDiq7oJjNym9LrpQnLLVZFSMW71ZMDTBmchF0GTFmtibx8Y0du1DdRIeNttmkfR9DeK1zoro-b3hEojA3gDx9L9eDpsEZs27v9UlkzdBZ_nU2SD5yHa4UfDuhn8t6Up654uWtQQBjqXQSKjZZ4X2KzQECqvsmOivij7kW5vgAovScnEYnXlGRq01fxAGwBSbrS6i-HBtn7iV9_OMOWgkHddKH2IjGHIZDQudXf4LFGmCjWTyO8lwnfo7MUTQaaEBE82cGh4h95_erw6oklJCyPc4sdPPnaUx_VlZ03yJCBVBEoc82kmF9x70Ii8MfaJR-1G7Jlz8kUFqLwPI-qRkQCcN73PDiaMHEqhd0wPsUBhpZr0HnapYTlXE0BJE4P8rObTcOIUS6wBqlSNzqFnJyHAJkB5EnAX4B7AGpqIb8C2hk9DvyW2qsNJpvjJ46zcRLJeFkoRbeqab-zDQyhPXmNEsxnCxdRaU10o2_9UyRpBo84uNzi9V5i9GtD29EsgTxh8HRTEPNP4_Rtw80Qwxj8zMctYEASIdSjN940Nt-4m5tb2z1SJkyKsTCVLLpo8AjQJqeSrISdoM9f9nFpvhmmnHLFTmtKqf0YZiJ4z3XDhlCBmpNAiNuzs-fJ19X6gmev0IEJT8usPFx2TDmbgBL2JPrnGekGBiNzZGN2gKO4WTu1i_IsW8dXGo4V6ywqAftmO4xJiuxe2P9KZYE2JjWcq4Shdl9x6zg5h0MY2OMGTDsmWjNe95TaEYUNw6L5KFbHE7K"}, {"type": "function_call", "name": "semantic_search_wikipedia", "arguments": "{\"query\":\"Australian raven adaptations to urban environments behavior diet nesting human settlements\"}", "call_id": "call_AQH4MJl0cJsNloVilbKLUOvy", "id": "fc_00c74ffe835d510a006ab36d1b759487d2867d24323dfce81a", "index": 1}]
-{"name": "semantic_search_wikipedia", "args": {"query": "Australian raven adaptations to urban environments behavior diet nesting human settlements"}, "id": "call_AQH4MJl0cJsNloVilbKLUOvy", "type": "tool_call"}</t>
+    <t>[{"id": "rs_0618e42c8eb6e5e4006ab4883fd56487d2ae6cb61615d1afd1", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtIhA0RlHjerZhUGwJmXmCizQHEvb_3GXOuJiS9aMPKpmea-6SV-Ee3Pa4nWhYFA32Hb3ynelAu8dKRiBVfQhPOf33qPy2p_cQtw1nrKePSLrvnZD24b_eRr2iYMO2KybzRYtCJzswRh17Bn_ZKS3bRjuHHJBgAuM6GtCR6E2u2eeJIPxFuswqxDNKhtAqJ9fu_3YFiHYRlcZBmb-Ds7qkVge0d45dNlkYLwMD4qyk7Ri-NnDg4jGI0aoiKMNM2DifOCSzC4JIXU5uEcLk2CznHex4AInVhpacFss8HqUiCy-2R1iw6YGdHLC9piGvP5K-hl6FV3xcGskPnKJzx_f-4p5eH9DaaDaTHsx1vzgGIpNg4Zaerk93OE0a342CxvfHT7ZN4iD41eNsoTpERIGsM4yazHdNainnE1CCIlyJdF4aMmN0omQ1K-AEvsBtYnm9jBHiZ_IJJWyJ5sHJ6DJujV_amAhJt9padgVxnkhg4Z5VWgxy2zASXfDKjo_yEzqkxxalnksQNfLfrKYuatbM2_x3iz1Jk0TkSnG5D0ACQDXUmQW2lL-oDHC6TB50r8h5FODc_YXmJaTFXsdIb9hKPKpgmFJ9k4w4jHvD_csr2TfiwUWgvoj-msOMdK5MkMg4lxpmyitFUt7Rxg0RMmpDOZqmKor9CbDOGcS5K1Gj7T445zzFOBllsUDD5GBDMHKgoZfsktX9KlfDgBYg2OyihxxgBxHCE3L3jaahdxMmKUycXjiDKs_bpgQKsOnHuOv-svjS10jc87YgSelR7rokAYw0lxh8EddGxDWi9xp0BvGlH-vi2w5iZ2DrQ2G7_VzYejc62M401gd8PxXe6vL9WrQFj3XsyVB0pPIAi68nUHKQ7DWFCDmeQPUmuUNGHSC6T5BmaB5N8MN4scHWHuD9dtyNLioQtyHmGJmQMNOH6EFnaGUVGnc0f1kb8dd2U7domagVtE4wUqkFzQ0cJIz0AuxIDqqZpHjMHRpFAqxe2HVCl7aybs3ahR3Zsd_vi56b83vZic7zq5ULy-9S6oDgkB4NHHWytQt7-HkEVKVrsZCzdFjOa5pecAWln6jEJQhTJoh-qeQaQ4WeLNMfNTwELUi83OMQn7n-hhQp1uCP1-Q8VH_mikzajsAs58BG-8EaQliV6mEomq8cX2cDyhQp1VKz6llMeY-BQzLqAjGmYwHZJ8EBZWGGlrEUwAPrdz_9Ybb"}, {"type": "function_call", "name": "semantic_search_wikipedia", "arguments": "{\"query\":\"Australian raven adaptations to urban environments behavior diet nesting cities human presence\"}", "call_id": "call_CYHCY65pl37MdkBkDceiC0jl", "id": "fc_0618e42c8eb6e5e4006ab48840272c87d2a19653a6d95eff40", "index": 1}]
+{"name": "semantic_search_wikipedia", "args": {"query": "Australian raven adaptations to urban environments behavior diet nesting cities human presence"}, "id": "call_CYHCY65pl37MdkBkDceiC0jl", "type": "tool_call"}</t>
   </si>
   <si>
     <t>Call total</t>
@@ -358,25 +358,25 @@
     <t>Tool · semantic_search_wikipedia</t>
   </si>
   <si>
-    <t>01a0cce2-3500-74c3-872b-438ccd8db4dc</t>
+    <t>01a0d134-3ccb-7261-b0ac-00b3d37b602b</t>
   </si>
   <si>
     <t xml:space="preserve">    Arguments</t>
   </si>
   <si>
-    <t>{'query': 'Australian raven adaptations to urban environments behavior diet nesting human settlements'}</t>
+    <t>{'query': 'Australian raven adaptations to urban environments behavior diet nesting cities human presence'}</t>
   </si>
   <si>
     <t xml:space="preserve">    Result</t>
   </si>
   <si>
-    <t>{"passages": [{"id": "passage-00016828", "text": "1827, its species name highlighting its similarity with the carrion crow ( c. corone ). two subspecies are recognised, which differ slightly in calls and are quite divergent genetically. the preferred habitat is open woodland and transitional zones. it has adapted well to urban environments and is a common city bird in sydney, canberra and perth. an omnivorous and opportunistic feeder, it eats a wide variety of plant and animal material, as well as food waste from urban areas. in eastern australia its range is strongly correlated with the presence of sheep, and it has been blamed for killing lambs. however, this is very rare, and the raven most often scavenges for afterbirth and stillborn animals as well as newborn lamb faeces. the australian raven is territorial, with pairs generally bonding for life. breeding takes place between july and september, with almost no variation across its range. the nest is a bowl @ - @ shaped structure of sticks sited high in a tree, or occasionally in a man @ - @ made structure such as a windmill or other building. = =", "license": "CC-BY-SA-3.0", "source_row": 49964, "token_start": 188, "title": "Australian raven", "token_end": 408, "source": "https://huggingface.co/datasets/Salesforce/wikitext/tree/b08601e04326c79dfdd32d625aee71d232d685c3/wikitext-103-raw-v1", "cosine_distance": 0.2472367286682129}, {"id": "passage-00016848", "text": "##worms are rarely eaten. australian ravens have been reported killing birds of such size as young galahs ( eolophus roseicapillus ) and starlings ( sturnus vulgaris ). most mammals are eaten as carrion, as many species are too large for the raven to kill, though young rabbits are a frequent prey item. australian ravens drink water frequently, up to ten times a day in hot weather. birds have been observed dunking pieces of meat in water before eating them, as well as doing the same with hard biscuits to make them soggy and soft. australian ravens are intelligent birds, and like many other corvids have innovative methods of seeking out food. foraging takes place in the early morning or late afternoon ; birds rest in the hotter part of the day. food is taken mainly from the ground, birds either finding objects while flying overhead, or by walking along and looking. however, they occasionally feed in trees \u2014 australian ravens forage eucalypt foliage for christmas beetles ( anoplognathus ), and devote a substantial amount of time to look", "token_start": 3948, "title": "Australian raven", "source_row": 49964, "token_end": 4168, "source": "https://huggingface.co/datasets/Salesforce/wikitext/tree/b08601e04326c79dfdd32d625aee71d232d685c3/wikitext-103-raw-v1", "license": "CC-BY-SA-3.0", "cosine_distance": 0.30797886848449707}, {"id": "passage-00016845", "text": "distinguishing australian corvids has hampered understanding of seasonal movements. the australian raven is thought to be largely sedentary, with most movement of over 16 km ( 9 @. @ 9 mi ) due to flocks of non @ - @ breeding subadult birds. juvenile birds leave their parents and join flocks when they are four or five months old. smaller flocks of 8 \u2013 30 birds stay within an area of around 260 square kilometres, while larger flocks of up to 300 birds may travel hundreds of kilometres seeking food. a single breeding pair and their brood can occupy a territory of up to around 120 hectares ( 300 acres ) and remains there year @ - @ round, though groups of ravens may enter this area to forage. australian ravens will defend their territory by chasing, dive @ - @ bombing and occasionally striking the backs of birds of prey, foxes or even people. they generally mate for life, though occasionally one male has been found to be mated with two females in adjacent territories. if the female dies, the male australian raven maintains the territory and finds another mate, while", "token_start": 3384, "source": "https://huggingface.co/datasets/Salesforce/wikitext/tree/b08601e04326c79dfdd32d625aee71d232d685c3/wikitext-103-raw-v1", "title": "Australian raven", "token_end": 3604, "license": "CC-BY-SA-3.0", "source_row": 49964, "cosine_distance": 0.3088942766189575}, {"id": "passage-00016847", "text": "neck. this takes place particularly in autumn, winter and spring, and is important in pair bonding. either member may initiate it, generally by landing near the other bird, shuffling next to its mate, then bending its head forward and presenting its nape. = = = feeding = = = the australian raven is omnivorous, though eats more meat than smaller corvids. its diet in summer contains a high proportion of insects, while more plant items are eaten in autumn. flesh makes up over half its diet in winter. invertebrates commonly eaten include spiders, millipedes, centipedes ( which ravens behead before eating ), grasshoppers, cicadas and caterpillars ( especially of the family noctuidae ), which are important in feeding nestlings. australian ravens sometimes eat yabbies ( cherax destructor ) from the edges of dams. unusually for a ground @ - @ feeding omnivore, earthworms are rarely eaten. australian ravens have been reported killing birds of such size as young galahs ( eolophus roseicapillus ) and starlings", "title": "Australian raven", "token_start": 3760, "token_end": 3980, "source_row": 49964, "source": "https://huggingface.co/datasets/Salesforce/wikitext/tree/b08601e04326c79dfdd32d625aee71d232d685c3/wikitext-103-raw-v1", "license": "CC-BY-SA-3.0", "cosine_distance": 0.31524449586868286}], "note": "Nearest passages are candidates, not proof of relevance; abstain if they do not answer the question."}</t>
+    <t>{"passages": [{"id": "passage-00016828", "text": "1827, its species name highlighting its similarity with the carrion crow ( c. corone ). two subspecies are recognised, which differ slightly in calls and are quite divergent genetically. the preferred habitat is open woodland and transitional zones. it has adapted well to urban environments and is a common city bird in sydney, canberra and perth. an omnivorous and opportunistic feeder, it eats a wide variety of plant and animal material, as well as food waste from urban areas. in eastern australia its range is strongly correlated with the presence of sheep, and it has been blamed for killing lambs. however, this is very rare, and the raven most often scavenges for afterbirth and stillborn animals as well as newborn lamb faeces. the australian raven is territorial, with pairs generally bonding for life. breeding takes place between july and september, with almost no variation across its range. the nest is a bowl @ - @ shaped structure of sticks sited high in a tree, or occasionally in a man @ - @ made structure such as a windmill or other building. = =", "title": "Australian raven", "license": "CC-BY-SA-3.0", "source_row": 49964, "token_end": 408, "source": "https://huggingface.co/datasets/Salesforce/wikitext/tree/b08601e04326c79dfdd32d625aee71d232d685c3/wikitext-103-raw-v1", "token_start": 188, "cosine_distance": 0.29102271795272827}, {"id": "passage-00016845", "text": "distinguishing australian corvids has hampered understanding of seasonal movements. the australian raven is thought to be largely sedentary, with most movement of over 16 km ( 9 @. @ 9 mi ) due to flocks of non @ - @ breeding subadult birds. juvenile birds leave their parents and join flocks when they are four or five months old. smaller flocks of 8 \u2013 30 birds stay within an area of around 260 square kilometres, while larger flocks of up to 300 birds may travel hundreds of kilometres seeking food. a single breeding pair and their brood can occupy a territory of up to around 120 hectares ( 300 acres ) and remains there year @ - @ round, though groups of ravens may enter this area to forage. australian ravens will defend their territory by chasing, dive @ - @ bombing and occasionally striking the backs of birds of prey, foxes or even people. they generally mate for life, though occasionally one male has been found to be mated with two females in adjacent territories. if the female dies, the male australian raven maintains the territory and finds another mate, while", "token_end": 3604, "source": "https://huggingface.co/datasets/Salesforce/wikitext/tree/b08601e04326c79dfdd32d625aee71d232d685c3/wikitext-103-raw-v1", "license": "CC-BY-SA-3.0", "token_start": 3384, "source_row": 49964, "title": "Australian raven", "cosine_distance": 0.34274810552597046}, {"id": "passage-00016848", "text": "##worms are rarely eaten. australian ravens have been reported killing birds of such size as young galahs ( eolophus roseicapillus ) and starlings ( sturnus vulgaris ). most mammals are eaten as carrion, as many species are too large for the raven to kill, though young rabbits are a frequent prey item. australian ravens drink water frequently, up to ten times a day in hot weather. birds have been observed dunking pieces of meat in water before eating them, as well as doing the same with hard biscuits to make them soggy and soft. australian ravens are intelligent birds, and like many other corvids have innovative methods of seeking out food. foraging takes place in the early morning or late afternoon ; birds rest in the hotter part of the day. food is taken mainly from the ground, birds either finding objects while flying overhead, or by walking along and looking. however, they occasionally feed in trees \u2014 australian ravens forage eucalypt foliage for christmas beetles ( anoplognathus ), and devote a substantial amount of time to look", "source": "https://huggingface.co/datasets/Salesforce/wikitext/tree/b08601e04326c79dfdd32d625aee71d232d685c3/wikitext-103-raw-v1", "license": "CC-BY-SA-3.0", "token_end": 4168, "source_row": 49964, "token_start": 3948, "title": "Australian raven", "cosine_distance": 0.3451145887374878}, {"id": "passage-00016847", "text": "neck. this takes place particularly in autumn, winter and spring, and is important in pair bonding. either member may initiate it, generally by landing near the other bird, shuffling next to its mate, then bending its head forward and presenting its nape. = = = feeding = = = the australian raven is omnivorous, though eats more meat than smaller corvids. its diet in summer contains a high proportion of insects, while more plant items are eaten in autumn. flesh makes up over half its diet in winter. invertebrates commonly eaten include spiders, millipedes, centipedes ( which ravens behead before eating ), grasshoppers, cicadas and caterpillars ( especially of the family noctuidae ), which are important in feeding nestlings. australian ravens sometimes eat yabbies ( cherax destructor ) from the edges of dams. unusually for a ground @ - @ feeding omnivore, earthworms are rarely eaten. australian ravens have been reported killing birds of such size as young galahs ( eolophus roseicapillus ) and starlings", "source_row": 49964, "title": "Australian raven", "license": "CC-BY-SA-3.0", "token_start": 3760, "token_end": 3980, "source": "https://huggingface.co/datasets/Salesforce/wikitext/tree/b08601e04326c79dfdd32d625aee71d232d685c3/wikitext-103-raw-v1", "cosine_distance": 0.36243724822998047}], "note": "Nearest passages are candidates, not proof of relevance; abstain if they do not answer the question."}</t>
   </si>
   <si>
     <t>R2</t>
   </si>
   <si>
-    <t>01a0cce2-361c-7c92-a6e3-3f28349a5186</t>
+    <t>01a0d134-3dd3-7be1-9a07-6c076d5c73bf</t>
   </si>
   <si>
     <t>Conversation history · cache read</t>
@@ -385,7 +385,7 @@
     <t xml:space="preserve">    Tool result</t>
   </si>
   <si>
-    <t>[{"id": "rs_00c74ffe835d510a006ab36d1cdd6c87d2b7c8ab0baff2fdba", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs20dAkpGdjLgTzLVBsV2VsFlNNBHMOdswyMgBCh2bQ3eQ3KBVeTuOb-K94sjVLNTQuMlpI--TCaHt6fj2ERM-fG0ag7Zn8AfEbbRyD2i29tv1-CgJT655SQdnb6MRrpxcqN9jBpQ6ufKCGlPiULHIrwLBMvbnPYUtemD4Jwb6zbgnLvQtAJiU8RGM458xYdyrnnowyZrs6RIbwGwigQS6CpW33kJ_tX6VQAk6COrjF6a7hIGpTx682c92nILYGRxmwMhZ4TEUZwc4ov5wiQ7jAsiw_k4jgLTw5VayfzN4IAAQAjd4RPbEd_W0T86-nRml1Z0Z_9V7grexesmNSpNjFHl3pnqdivcxjE36rknuWfDrCW7hLBGNrpjvW-OYx34MdXGKpPdeEkcW6Cq2ZMmGWRbsowfAj-aBJ6AZ1Tl9oM6gMWgawGBdabAsPz5BSi-PBDyoi_7UAwbYH_zb_cwHIRhLvP_Fj8lgBZnPOl1odIHCx3kohEClqXxgR7CKUSEtDp85K41pUst6tET0atKtwnDSuVL2hS8clcJ_Q7RTcVMmzOsU6CEXno66sYJ_XuHXfysewMmVRkJDkWySPZi2lVTa8eUPy9RHJtQrtiyQ9LhoOsQ1YGxzez8TcxMvSQweRcuaW9lfZjWm-0wUa6Z7gWuADdDTl75ScTVJJvT_W9wXn1BCgdQlbqt-7MU_Flhj_RrYi9OdUz4FEmKISfN35xt1H8EL-oQzKt7XWN6XnOru73DPCJz9i_9HngXFjA-ljWv7LhF3N7FkULoSqY9LGrfaHqRMx1jkJZVQJgcZd9Ksq9SDH-K-g0-g4msEyCyRJVtY5yF3Gso66MjfqwCw__GdaKXnZhVsll92fudcHEqN66HDpzDR5pEt4sNzq2wWgtyxmchn_07M0AFMqN24r4ZpoL9CrMnXw0UgJIEKAACfmilcljTeZKlPupBoX0RdJs4pKhsCiMezb-nmv7FuXkL5dui8605teZtgHPeS3kBREw9lb67RfyRL0Zfu4XuBIU0LY65EIJ8w5XFg6Y2RVq_2ruagLiyaRGFVCd64aTvxgJCQulzN_zHSKReKTiCyzIko9wUwumcIE8ksR1Fo5AxudHSmZaspWB-AP0wqtbLju6E3uNBtD4vES-uDlzYxxqfl-woNcOMSkisxpx7CPhOCilYRjeB-gasXtNjrabpCMPf-pyBv3eSdzksyi-yqsLtJy0dG0lzGOG5IuFjT6D-ZWibB6cFnJhI68XBuyvb3KP_y5T5Vt3zURF4dvTbHILtyIDjtsj5ZFUiaEhSfHg8LISX105NENLkxZaAGNRk6pI-LQB3I0eLTCmu4xRCtJy7btd5jQjjTIMEAGRsWKWt5ZOnMVI2ZgJV5OeoFaOVE0KksoBvTuPJ048390i7zZIfufpCminCnpCTOFrQrSwdL_yYf7VcX4s0MMqYaHsIgkc8oQwSAvKDi7lNYdri8ljd1fdT-29l9NV_Ra1QnKSDivWevkpXPSAZ22oyt1IfxeNgRLvZ8ZeNbCkPBNyYyNilwk_nlfi6ak4SM3XuH1P4Kg=="}, {"type": "text", "text": "The Australian raven has adapted to cities in several ways:\n\n- **Flexible diet:** It is an omnivorous, opportunistic feeder and readily scavenges **food waste** in urban areas. [passage-00016828]\n- **Use of built structures:** Although it usually nests high in trees, it can also nest on **man-made structures**, including windmills and buildings. [passage-00016828]\n- **Tolerance of urban living:** These adaptations have enabled it to become a **common city bird** in Sydney, Canberra, and Perth. [passage-00016828]\n\nThe indexed evidence supports these points, but does not provide much detail on other possible urban adaptations, such as changes in nesting timing or responses to traffic and human disturbance.", "phase": "final_answer", "index": 1, "id": "msg_00c74ffe835d510a006ab36d1d895487d2ae5930ead501cf96"}]</t>
+    <t>[{"type": "text", "text": "The Australian raven has adapted to urban environments in several ways:\n\n- **Flexible diet:** It is an opportunistic omnivore, eating varied plant and animal matter as well as **food waste** from urban areas. [passage-00016828]\n- **Use of human structures:** Although it usually nests high in trees, it may also build nests on **man-made structures**, including windmills and other buildings. [passage-00016828]\n- **Behavioral flexibility:** Its intelligence and innovative foraging methods help it locate and exploit new food sources. [passage-00016848]\n- **Urban tolerance:** These adaptations have enabled it to become a common city bird in **Sydney, Canberra, and Perth**. [passage-00016828]\n\nThe indexed passages support these adaptations, but do not provide detailed evidence about other possible urban changes, such as altered calls, traffic avoidance, or changes in breeding success.", "phase": "final_answer", "index": 0, "id": "msg_0618e42c8eb6e5e4006ab48841b11487d2b4ee50c8bb0eb34f"}]</t>
   </si>
   <si>
     <t>wikipedia_rag_agent</t>
@@ -406,7 +406,7 @@
     <t>Prepare the current conversation, run model middleware, and invoke the chat model.</t>
   </si>
   <si>
-    <t>01a0cce2-2de6-7af2-81fa-f7556940a1e3</t>
+    <t>01a0d134-3662-7413-acc6-513f2ab0a705</t>
   </si>
   <si>
     <t xml:space="preserve">        ChatOpenAI</t>
@@ -427,7 +427,7 @@
     <t>Execute tool calls requested by the preceding model response and return their observations.</t>
   </si>
   <si>
-    <t>01a0cce2-34ff-7452-bcb0-c562b10c3022</t>
+    <t>01a0d134-3cca-7f33-ac39-c5e3e40bd955</t>
   </si>
   <si>
     <t>No model charge</t>
@@ -443,7 +443,7 @@
 passages are candidates; check relevance before using them as evidence.</t>
   </si>
   <si>
-    <t>01a0cce2-361b-79c2-a53f-02049fba08f5</t>
+    <t>01a0d134-3dd2-7d90-8469-48a08bc204e1</t>
   </si>
 </sst>
 </file>
@@ -850,7 +850,7 @@
   <sheetPr>
     <tabColor rgb="FF173B70"/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -910,20 +910,20 @@
         <v>91</v>
       </c>
       <c r="E2" s="2">
-        <f>IF(COUNT('Turns'!E17,'Turns'!E33)=2,SUM('Turns'!E17,'Turns'!E33),"Unknown")</f>
-        <v>0.000668671605</v>
+        <f>IF(COUNT('Turns'!E17,'Turns'!E32)=2,SUM('Turns'!E17,'Turns'!E32),"Unknown")</f>
+        <v>0.0006467024825</v>
       </c>
       <c r="F2" s="2">
-        <f>IF(COUNT('Turns'!F17,'Turns'!F33)=2,SUM('Turns'!F17,'Turns'!F33),"Unknown")</f>
-        <v>0.0007665</v>
+        <f>IF(COUNT('Turns'!F17,'Turns'!F32)=2,SUM('Turns'!F17,'Turns'!F32),"Unknown")</f>
+        <v>0.00073795</v>
       </c>
       <c r="G2" s="5">
         <f>IF(ISNUMBER(E2),ROUND(E2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>67.0</v>
+        <v>65.0</v>
       </c>
       <c r="H2" s="5">
         <f>IF(ISNUMBER(F2),ROUND(F2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>77.0</v>
+        <v>74.0</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -934,20 +934,20 @@
         <v>92</v>
       </c>
       <c r="E3" s="2">
-        <f>IF(COUNT('Turns'!E17,'Turns'!E33)=2,SUM('Turns'!E17,'Turns'!E33),"Unknown")</f>
-        <v>0.000668671605</v>
+        <f>IF(COUNT('Turns'!E17,'Turns'!E32)=2,SUM('Turns'!E17,'Turns'!E32),"Unknown")</f>
+        <v>0.0006467024825</v>
       </c>
       <c r="F3" s="2">
-        <f>IF(COUNT('Turns'!F17,'Turns'!F33)=2,SUM('Turns'!F17,'Turns'!F33),"Unknown")</f>
-        <v>0.0007665</v>
+        <f>IF(COUNT('Turns'!F17,'Turns'!F32)=2,SUM('Turns'!F17,'Turns'!F32),"Unknown")</f>
+        <v>0.00073795</v>
       </c>
       <c r="G3" s="5">
         <f>IF(ISNUMBER(E3),ROUND(E3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>67.0</v>
+        <v>65.0</v>
       </c>
       <c r="H3" s="5">
         <f>IF(ISNUMBER(F3),ROUND(F3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>77.0</v>
+        <v>74.0</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -985,7 +985,7 @@
       </c>
       <c r="E5" s="2">
         <f>IF(AND(ISNUMBER(F5),ISNUMBER('Reference data'!$B$3)),F5*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.2975586e-05</v>
+        <v>3.312603e-05</v>
       </c>
       <c r="F5" s="2">
         <f>IF(D5=0,0,IF(ISNUMBER('Reference data'!B17),D5*'Reference data'!B17/1000000,"Unknown"))</f>
@@ -1072,7 +1072,7 @@
         <v>105</v>
       </c>
       <c r="D11" s="4">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="24" customHeight="1">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="E12" s="2">
         <f>IF(AND(ISNUMBER(F12),ISNUMBER('Reference data'!$B$3)),F12*'Reference data'!$B$3,"Unknown")</f>
-        <v>9.421596e-06</v>
+        <v>9.46458e-06</v>
       </c>
       <c r="F12" s="2">
         <f>IF(D12=0,0,IF(ISNUMBER('Reference data'!F17),D12*'Reference data'!F17/1000000,"Unknown"))</f>
@@ -1116,15 +1116,15 @@
         <v>107</v>
       </c>
       <c r="D13" s="5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E13" s="2">
         <f>IF(AND(ISNUMBER(F13),ISNUMBER('Reference data'!$B$3)),F13*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.3499008e-05</v>
+        <v>3.470346e-05</v>
       </c>
       <c r="F13" s="2">
         <f>IF(D13=0,0,IF(ISNUMBER('Reference data'!E17),D13*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>3.84e-05</v>
+        <v>3.96e-05</v>
       </c>
       <c r="G13" s="5">
         <f>IF(ISNUMBER(E13),ROUND(E13*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1183,11 +1183,11 @@
       </c>
       <c r="E17" s="2">
         <f>IF(COUNT('Turns'!E5,'Turns'!E12,'Turns'!E13)=3,SUM('Turns'!E5,'Turns'!E12,'Turns'!E13),"Unknown")</f>
-        <v>7.589619e-05</v>
+        <v>7.729407e-05</v>
       </c>
       <c r="F17" s="2">
         <f>IF(COUNT('Turns'!F5,'Turns'!F12,'Turns'!F13)=3,SUM('Turns'!F5,'Turns'!F12,'Turns'!F13),"Unknown")</f>
-        <v>8.7e-05</v>
+        <v>8.82e-05</v>
       </c>
       <c r="G17" s="5">
         <f>IF(ISNUMBER(E17),ROUND(E17*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1248,7 +1248,7 @@
         <v>94</v>
       </c>
       <c r="D21" s="4">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>95</v>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="E23" s="2">
         <f>IF(AND(ISNUMBER(F23),ISNUMBER('Reference data'!$B$3)),F23*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.23422e-07</v>
+        <v>5.2581e-07</v>
       </c>
       <c r="F23" s="2">
         <f>IF(D23=0,0,IF(ISNUMBER('Reference data'!B17),D23*'Reference data'!B17/1000000,"Unknown"))</f>
@@ -1342,15 +1342,15 @@
         <v>103</v>
       </c>
       <c r="D25" s="5">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="E25" s="2">
         <f>IF(AND(ISNUMBER(F25),ISNUMBER('Reference data'!$B$3)),F25*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.000365086845</v>
+        <v>0.0003669715625</v>
       </c>
       <c r="F25" s="2">
         <f>IF(D25=0,0,IF(ISNUMBER('Reference data'!D17),D25*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>0.0004185</v>
+        <v>0.00041875</v>
       </c>
       <c r="G25" s="5">
         <f>IF(ISNUMBER(E25),ROUND(E25*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1383,7 +1383,7 @@
         <v>105</v>
       </c>
       <c r="D27" s="4">
-        <v>217</v>
+        <v>192</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="24" customHeight="1">
@@ -1394,29 +1394,29 @@
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D28" s="5">
-        <v>57</v>
+        <v>192</v>
       </c>
       <c r="E28" s="2">
         <f>IF(AND(ISNUMBER(F28),ISNUMBER('Reference data'!$B$3)),F28*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.9670108e-05</v>
+        <v>0.00020191104</v>
       </c>
       <c r="F28" s="2">
-        <f>IF(D28=0,0,IF(ISNUMBER('Reference data'!F17),D28*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>6.84e-05</v>
+        <f>IF(D28=0,0,IF(ISNUMBER('Reference data'!E17),D28*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>0.0002304</v>
       </c>
       <c r="G28" s="5">
         <f>IF(ISNUMBER(E28),ROUND(E28*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
+        <v>20.0</v>
       </c>
       <c r="H28" s="5">
         <f>IF(ISNUMBER(F28),ROUND(F28*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="24" customHeight="1">
+        <v>23.0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="164" customHeight="1">
       <c r="A29" t="s">
         <v>118</v>
       </c>
@@ -1424,29 +1424,13 @@
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>107</v>
-      </c>
-      <c r="D29" s="5">
-        <v>160</v>
-      </c>
-      <c r="E29" s="2">
-        <f>IF(AND(ISNUMBER(F29),ISNUMBER('Reference data'!$B$3)),F29*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.00016749504</v>
-      </c>
-      <c r="F29" s="2">
-        <f>IF(D29=0,0,IF(ISNUMBER('Reference data'!E17),D29*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>0.000192</v>
-      </c>
-      <c r="G29" s="5">
-        <f>IF(ISNUMBER(E29),ROUND(E29*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>17.0</v>
-      </c>
-      <c r="H29" s="5">
-        <f>IF(ISNUMBER(F29),ROUND(F29*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>19.0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="398" customHeight="1">
+        <v>108</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="24" customHeight="1">
       <c r="A30" t="s">
         <v>118</v>
       </c>
@@ -1454,10 +1438,7 @@
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>108</v>
-      </c>
-      <c r="I30" s="6" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="24" customHeight="1">
@@ -1468,52 +1449,41 @@
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="24" customHeight="1">
-      <c r="A32" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A32" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="B32">
-        <v>1</v>
-      </c>
-      <c r="C32" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A33" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="B33" s="4">
-        <v>1</v>
-      </c>
-      <c r="C33" s="4" t="s">
+      <c r="B32" s="4">
+        <v>1</v>
+      </c>
+      <c r="C32" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="E33" s="2">
-        <f>IF(COUNT('Turns'!E22,'Turns'!E23,'Turns'!E25,'Turns'!E28,'Turns'!E29)=5,SUM('Turns'!E22,'Turns'!E23,'Turns'!E25,'Turns'!E28,'Turns'!E29),"Unknown")</f>
-        <v>0.000592775415</v>
-      </c>
-      <c r="F33" s="2">
-        <f>IF(COUNT('Turns'!F22,'Turns'!F23,'Turns'!F25,'Turns'!F28,'Turns'!F29)=5,SUM('Turns'!F22,'Turns'!F23,'Turns'!F25,'Turns'!F28,'Turns'!F29),"Unknown")</f>
-        <v>0.0006795</v>
-      </c>
-      <c r="G33" s="5">
-        <f>IF(ISNUMBER(E33),ROUND(E33*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>59.0</v>
-      </c>
-      <c r="H33" s="5">
-        <f>IF(ISNUMBER(F33),ROUND(F33*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>68.0</v>
-      </c>
-      <c r="K33" s="4" t="s">
+      <c r="E32" s="2">
+        <f>IF(COUNT('Turns'!E22,'Turns'!E23,'Turns'!E25,'Turns'!E28)=4,SUM('Turns'!E22,'Turns'!E23,'Turns'!E25,'Turns'!E28),"Unknown")</f>
+        <v>0.0005694084125</v>
+      </c>
+      <c r="F32" s="2">
+        <f>IF(COUNT('Turns'!F22,'Turns'!F23,'Turns'!F25,'Turns'!F28)=4,SUM('Turns'!F22,'Turns'!F23,'Turns'!F25,'Turns'!F28),"Unknown")</f>
+        <v>0.00064975</v>
+      </c>
+      <c r="G32" s="5">
+        <f>IF(ISNUMBER(E32),ROUND(E32*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>57.0</v>
+      </c>
+      <c r="H32" s="5">
+        <f>IF(ISNUMBER(F32),ROUND(F32*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>65.0</v>
+      </c>
+      <c r="K32" s="4" t="s">
         <v>111</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:AE33">
+  <conditionalFormatting sqref="A2:AE32">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$K2="error"</formula>
     </cfRule>
@@ -1660,7 +1630,7 @@
       </c>
       <c r="K2" s="2">
         <f>IF(COUNT('Turns'!E5,'Turns'!E23)=2,SUM('Turns'!E5,'Turns'!E23),"Unknown")</f>
-        <v>3.3499008e-05</v>
+        <v>3.365184e-05</v>
       </c>
       <c r="L2" s="2">
         <f>IF(COUNT('Turns'!F5,'Turns'!F23)=2,SUM('Turns'!F5,'Turns'!F23),"Unknown")</f>
@@ -1680,58 +1650,58 @@
       </c>
       <c r="P2" s="2">
         <f>IF(COUNT('Turns'!D25)=1,SUM('Turns'!D25),"Unknown")</f>
-        <v>1674.0</v>
+        <v>1675.0</v>
       </c>
       <c r="Q2" s="2">
         <f>IF(COUNT('Turns'!E25)=1,SUM('Turns'!E25),"Unknown")</f>
-        <v>0.000365086845</v>
+        <v>0.0003669715625</v>
       </c>
       <c r="R2" s="2">
         <f>IF(COUNT('Turns'!F25)=1,SUM('Turns'!F25),"Unknown")</f>
-        <v>0.0004185</v>
+        <v>0.00041875</v>
       </c>
       <c r="S2" s="2">
-        <f>IF(COUNT('Turns'!D13,'Turns'!D29)=2,SUM('Turns'!D13,'Turns'!D29),"Unknown")</f>
-        <v>192.0</v>
+        <f>IF(COUNT('Turns'!D13,'Turns'!D28)=2,SUM('Turns'!D13,'Turns'!D28),"Unknown")</f>
+        <v>225.0</v>
       </c>
       <c r="T2" s="2">
-        <f>IF(COUNT('Turns'!E13,'Turns'!E29)=2,SUM('Turns'!E13,'Turns'!E29),"Unknown")</f>
-        <v>0.000200994048</v>
+        <f>IF(COUNT('Turns'!E13,'Turns'!E28)=2,SUM('Turns'!E13,'Turns'!E28),"Unknown")</f>
+        <v>0.0002366145</v>
       </c>
       <c r="U2" s="2">
-        <f>IF(COUNT('Turns'!F13,'Turns'!F29)=2,SUM('Turns'!F13,'Turns'!F29),"Unknown")</f>
-        <v>0.0002304</v>
+        <f>IF(COUNT('Turns'!F13,'Turns'!F28)=2,SUM('Turns'!F13,'Turns'!F28),"Unknown")</f>
+        <v>0.00027</v>
       </c>
       <c r="V2" s="2">
-        <f>IF(COUNT('Turns'!D12,'Turns'!D28)=2,SUM('Turns'!D12,'Turns'!D28),"Unknown")</f>
-        <v>66.0</v>
+        <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
+        <v>9.0</v>
       </c>
       <c r="W2" s="2">
-        <f>IF(COUNT('Turns'!E12,'Turns'!E28)=2,SUM('Turns'!E12,'Turns'!E28),"Unknown")</f>
-        <v>6.9091704e-05</v>
+        <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
+        <v>9.46458e-06</v>
       </c>
       <c r="X2" s="2">
-        <f>IF(COUNT('Turns'!F12,'Turns'!F28)=2,SUM('Turns'!F12,'Turns'!F28),"Unknown")</f>
-        <v>7.92e-05</v>
+        <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
+        <v>1.08e-05</v>
       </c>
       <c r="Y2" s="2">
-        <f>IF(COUNT('Turns'!E17,'Turns'!E33)=2,SUM('Turns'!E17,'Turns'!E33),"Unknown")</f>
-        <v>0.000668671605</v>
+        <f>IF(COUNT('Turns'!E17,'Turns'!E32)=2,SUM('Turns'!E17,'Turns'!E32),"Unknown")</f>
+        <v>0.0006467024825</v>
       </c>
       <c r="Z2" s="2">
-        <f>IF(COUNT('Turns'!F17,'Turns'!F33)=2,SUM('Turns'!F17,'Turns'!F33),"Unknown")</f>
-        <v>0.0007665</v>
+        <f>IF(COUNT('Turns'!F17,'Turns'!F32)=2,SUM('Turns'!F17,'Turns'!F32),"Unknown")</f>
+        <v>0.00073795</v>
       </c>
       <c r="AA2" s="5">
         <f>IF(ISNUMBER(Y2),ROUND(Y2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>67.0</v>
+        <v>65.0</v>
       </c>
       <c r="AB2" s="5">
         <f>IF(ISNUMBER(Z2),ROUND(Z2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>77.0</v>
+        <v>74.0</v>
       </c>
       <c r="AD2" s="1">
-        <v>4821.405</v>
+        <v>5029.036</v>
       </c>
       <c r="AE2" s="1" t="s">
         <v>126</v>
@@ -1768,7 +1738,7 @@
       </c>
       <c r="K3" s="2">
         <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>3.2975586e-05</v>
+        <v>3.312603e-05</v>
       </c>
       <c r="L3" s="2">
         <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
@@ -1794,15 +1764,15 @@
       </c>
       <c r="S3" s="2">
         <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
       <c r="T3" s="2">
         <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>3.3499008e-05</v>
+        <v>3.470346e-05</v>
       </c>
       <c r="U3" s="2">
         <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
-        <v>3.84e-05</v>
+        <v>3.96e-05</v>
       </c>
       <c r="V3" s="2">
         <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
@@ -1810,7 +1780,7 @@
       </c>
       <c r="W3" s="2">
         <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>9.421596e-06</v>
+        <v>9.46458e-06</v>
       </c>
       <c r="X3" s="2">
         <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
@@ -1818,11 +1788,11 @@
       </c>
       <c r="Y3" s="2">
         <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>7.589619e-05</v>
+        <v>7.729407e-05</v>
       </c>
       <c r="Z3" s="2">
         <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>8.7e-05</v>
+        <v>8.82e-05</v>
       </c>
       <c r="AA3" s="5">
         <f>IF(ISNUMBER(Y3),ROUND(Y3*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1833,7 +1803,7 @@
         <v>9.0</v>
       </c>
       <c r="AD3" s="1">
-        <v>1816.119</v>
+        <v>1639.068</v>
       </c>
       <c r="AE3" s="1" t="s">
         <v>126</v>
@@ -1873,7 +1843,7 @@
       </c>
       <c r="K4" s="2">
         <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>3.2975586e-05</v>
+        <v>3.312603e-05</v>
       </c>
       <c r="L4" s="2">
         <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
@@ -1899,15 +1869,15 @@
       </c>
       <c r="S4" s="2">
         <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
       <c r="T4" s="2">
         <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>3.3499008e-05</v>
+        <v>3.470346e-05</v>
       </c>
       <c r="U4" s="2">
         <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
-        <v>3.84e-05</v>
+        <v>3.96e-05</v>
       </c>
       <c r="V4" s="2">
         <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
@@ -1915,7 +1885,7 @@
       </c>
       <c r="W4" s="2">
         <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>9.421596e-06</v>
+        <v>9.46458e-06</v>
       </c>
       <c r="X4" s="2">
         <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
@@ -1923,11 +1893,11 @@
       </c>
       <c r="Y4" s="2">
         <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>7.589619e-05</v>
+        <v>7.729407e-05</v>
       </c>
       <c r="Z4" s="2">
         <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>8.7e-05</v>
+        <v>8.82e-05</v>
       </c>
       <c r="AA4" s="5">
         <f>IF(ISNUMBER(Y4),ROUND(Y4*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1941,7 +1911,7 @@
         <v>93</v>
       </c>
       <c r="AD4" s="1">
-        <v>1813.714</v>
+        <v>1636.7</v>
       </c>
       <c r="AE4" s="1" t="s">
         <v>133</v>
@@ -1973,7 +1943,7 @@
         <v>49</v>
       </c>
       <c r="AD5" s="1">
-        <v>282.83</v>
+        <v>262.725</v>
       </c>
       <c r="AE5" s="1" t="s">
         <v>137</v>
@@ -2005,7 +1975,7 @@
         <v>136</v>
       </c>
       <c r="AD6" s="1">
-        <v>280.309</v>
+        <v>260.596</v>
       </c>
       <c r="AE6" s="1" t="s">
         <v>137</v>
@@ -2042,7 +2012,7 @@
       </c>
       <c r="K7" s="2">
         <f>IF(COUNT('Turns'!E23)=1,SUM('Turns'!E23),"Unknown")</f>
-        <v>5.23422e-07</v>
+        <v>5.2581e-07</v>
       </c>
       <c r="L7" s="2">
         <f>IF(COUNT('Turns'!F23)=1,SUM('Turns'!F23),"Unknown")</f>
@@ -2062,58 +2032,55 @@
       </c>
       <c r="P7" s="2">
         <f>IF(COUNT('Turns'!D25)=1,SUM('Turns'!D25),"Unknown")</f>
-        <v>1674.0</v>
+        <v>1675.0</v>
       </c>
       <c r="Q7" s="2">
         <f>IF(COUNT('Turns'!E25)=1,SUM('Turns'!E25),"Unknown")</f>
-        <v>0.000365086845</v>
+        <v>0.0003669715625</v>
       </c>
       <c r="R7" s="2">
         <f>IF(COUNT('Turns'!F25)=1,SUM('Turns'!F25),"Unknown")</f>
-        <v>0.0004185</v>
+        <v>0.00041875</v>
       </c>
       <c r="S7" s="2">
-        <f>IF(COUNT('Turns'!D29)=1,SUM('Turns'!D29),"Unknown")</f>
-        <v>160.0</v>
+        <f>IF(COUNT('Turns'!D28)=1,SUM('Turns'!D28),"Unknown")</f>
+        <v>192.0</v>
       </c>
       <c r="T7" s="2">
-        <f>IF(COUNT('Turns'!E29)=1,SUM('Turns'!E29),"Unknown")</f>
-        <v>0.00016749504</v>
+        <f>IF(COUNT('Turns'!E28)=1,SUM('Turns'!E28),"Unknown")</f>
+        <v>0.00020191104</v>
       </c>
       <c r="U7" s="2">
-        <f>IF(COUNT('Turns'!F29)=1,SUM('Turns'!F29),"Unknown")</f>
-        <v>0.000192</v>
+        <f>IF(COUNT('Turns'!F28)=1,SUM('Turns'!F28),"Unknown")</f>
+        <v>0.0002304</v>
       </c>
       <c r="V7" s="2">
-        <f>IF(COUNT('Turns'!D28)=1,SUM('Turns'!D28),"Unknown")</f>
-        <v>57.0</v>
+        <v>0</v>
       </c>
       <c r="W7" s="2">
-        <f>IF(COUNT('Turns'!E28)=1,SUM('Turns'!E28),"Unknown")</f>
-        <v>5.9670108e-05</v>
+        <v>0</v>
       </c>
       <c r="X7" s="2">
-        <f>IF(COUNT('Turns'!F28)=1,SUM('Turns'!F28),"Unknown")</f>
-        <v>6.84e-05</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="2">
-        <f>IF(COUNT('Turns'!E33)=1,SUM('Turns'!E33),"Unknown")</f>
-        <v>0.000592775415</v>
+        <f>IF(COUNT('Turns'!E32)=1,SUM('Turns'!E32),"Unknown")</f>
+        <v>0.0005694084125</v>
       </c>
       <c r="Z7" s="2">
-        <f>IF(COUNT('Turns'!F33)=1,SUM('Turns'!F33),"Unknown")</f>
-        <v>0.0006795</v>
+        <f>IF(COUNT('Turns'!F32)=1,SUM('Turns'!F32),"Unknown")</f>
+        <v>0.00064975</v>
       </c>
       <c r="AA7" s="5">
         <f>IF(ISNUMBER(Y7),ROUND(Y7*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>59.0</v>
+        <v>57.0</v>
       </c>
       <c r="AB7" s="5">
         <f>IF(ISNUMBER(Z7),ROUND(Z7*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>68.0</v>
+        <v>65.0</v>
       </c>
       <c r="AD7" s="1">
-        <v>2717.693</v>
+        <v>3121.866</v>
       </c>
       <c r="AE7" s="1" t="s">
         <v>126</v>
@@ -2136,7 +2103,7 @@
         <v>111</v>
       </c>
       <c r="F8" s="1">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>132</v>
@@ -2153,7 +2120,7 @@
       </c>
       <c r="K8" s="2">
         <f>IF(COUNT('Turns'!E23)=1,SUM('Turns'!E23),"Unknown")</f>
-        <v>5.23422e-07</v>
+        <v>5.2581e-07</v>
       </c>
       <c r="L8" s="2">
         <f>IF(COUNT('Turns'!F23)=1,SUM('Turns'!F23),"Unknown")</f>
@@ -2173,61 +2140,58 @@
       </c>
       <c r="P8" s="2">
         <f>IF(COUNT('Turns'!D25)=1,SUM('Turns'!D25),"Unknown")</f>
-        <v>1674.0</v>
+        <v>1675.0</v>
       </c>
       <c r="Q8" s="2">
         <f>IF(COUNT('Turns'!E25)=1,SUM('Turns'!E25),"Unknown")</f>
-        <v>0.000365086845</v>
+        <v>0.0003669715625</v>
       </c>
       <c r="R8" s="2">
         <f>IF(COUNT('Turns'!F25)=1,SUM('Turns'!F25),"Unknown")</f>
-        <v>0.0004185</v>
+        <v>0.00041875</v>
       </c>
       <c r="S8" s="2">
-        <f>IF(COUNT('Turns'!D29)=1,SUM('Turns'!D29),"Unknown")</f>
-        <v>160.0</v>
+        <f>IF(COUNT('Turns'!D28)=1,SUM('Turns'!D28),"Unknown")</f>
+        <v>192.0</v>
       </c>
       <c r="T8" s="2">
-        <f>IF(COUNT('Turns'!E29)=1,SUM('Turns'!E29),"Unknown")</f>
-        <v>0.00016749504</v>
+        <f>IF(COUNT('Turns'!E28)=1,SUM('Turns'!E28),"Unknown")</f>
+        <v>0.00020191104</v>
       </c>
       <c r="U8" s="2">
-        <f>IF(COUNT('Turns'!F29)=1,SUM('Turns'!F29),"Unknown")</f>
-        <v>0.000192</v>
+        <f>IF(COUNT('Turns'!F28)=1,SUM('Turns'!F28),"Unknown")</f>
+        <v>0.0002304</v>
       </c>
       <c r="V8" s="2">
-        <f>IF(COUNT('Turns'!D28)=1,SUM('Turns'!D28),"Unknown")</f>
-        <v>57.0</v>
+        <v>0</v>
       </c>
       <c r="W8" s="2">
-        <f>IF(COUNT('Turns'!E28)=1,SUM('Turns'!E28),"Unknown")</f>
-        <v>5.9670108e-05</v>
+        <v>0</v>
       </c>
       <c r="X8" s="2">
-        <f>IF(COUNT('Turns'!F28)=1,SUM('Turns'!F28),"Unknown")</f>
-        <v>6.84e-05</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="2">
-        <f>IF(COUNT('Turns'!E33)=1,SUM('Turns'!E33),"Unknown")</f>
-        <v>0.000592775415</v>
+        <f>IF(COUNT('Turns'!E32)=1,SUM('Turns'!E32),"Unknown")</f>
+        <v>0.0005694084125</v>
       </c>
       <c r="Z8" s="2">
-        <f>IF(COUNT('Turns'!F33)=1,SUM('Turns'!F33),"Unknown")</f>
-        <v>0.0006795</v>
+        <f>IF(COUNT('Turns'!F32)=1,SUM('Turns'!F32),"Unknown")</f>
+        <v>0.00064975</v>
       </c>
       <c r="AA8" s="5">
         <f>IF(ISNUMBER(Y8),ROUND(Y8*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>59.0</v>
+        <v>57.0</v>
       </c>
       <c r="AB8" s="5">
         <f>IF(ISNUMBER(Z8),ROUND(Z8*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>68.0</v>
+        <v>65.0</v>
       </c>
       <c r="AC8" s="1" t="s">
         <v>118</v>
       </c>
       <c r="AD8" s="1">
-        <v>2715.842</v>
+        <v>3119.307</v>
       </c>
       <c r="AE8" s="1" t="s">
         <v>133</v>
@@ -2285,7 +2249,7 @@
         <v>43</v>
       </c>
       <c r="B3" s="2">
-        <v>0.87237</v>
+        <v>0.87635</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>44</v>

--- a/reports/rag_chat/report.xlsx
+++ b/reports/rag_chat/report.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="142">
   <si>
     <t>Request</t>
   </si>
@@ -165,7 +165,7 @@
     <t>Run ID</t>
   </si>
   <si>
-    <t>01a0d134-365e-7531-a1be-bfe2a5d9498f</t>
+    <t>01a0d586-d0ba-7d32-9f2b-fe5b610c4034</t>
   </si>
   <si>
     <t>Recording</t>
@@ -177,13 +177,13 @@
     <t>FX reference date</t>
   </si>
   <si>
-    <t>2026-09-23</t>
+    <t>2026-09-24</t>
   </si>
   <si>
     <t>FX fetched at</t>
   </si>
   <si>
-    <t>2026-09-24T02:09:35.117183Z</t>
+    <t>2026-09-24T22:21:31.719587Z</t>
   </si>
   <si>
     <t>UTC</t>
@@ -306,7 +306,7 @@
     <t>gpt-5.6-luna</t>
   </si>
   <si>
-    <t>01a0d134-3663-7130-a324-ff0cb990ac3b</t>
+    <t>01a0d586-d0be-76b3-af7e-27072339a3ed</t>
   </si>
   <si>
     <t>Input at standard rate</t>
@@ -345,8 +345,8 @@
     <t xml:space="preserve">    Output content</t>
   </si>
   <si>
-    <t>[{"id": "rs_0618e42c8eb6e5e4006ab4883fd56487d2ae6cb61615d1afd1", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtIhA0RlHjerZhUGwJmXmCizQHEvb_3GXOuJiS9aMPKpmea-6SV-Ee3Pa4nWhYFA32Hb3ynelAu8dKRiBVfQhPOf33qPy2p_cQtw1nrKePSLrvnZD24b_eRr2iYMO2KybzRYtCJzswRh17Bn_ZKS3bRjuHHJBgAuM6GtCR6E2u2eeJIPxFuswqxDNKhtAqJ9fu_3YFiHYRlcZBmb-Ds7qkVge0d45dNlkYLwMD4qyk7Ri-NnDg4jGI0aoiKMNM2DifOCSzC4JIXU5uEcLk2CznHex4AInVhpacFss8HqUiCy-2R1iw6YGdHLC9piGvP5K-hl6FV3xcGskPnKJzx_f-4p5eH9DaaDaTHsx1vzgGIpNg4Zaerk93OE0a342CxvfHT7ZN4iD41eNsoTpERIGsM4yazHdNainnE1CCIlyJdF4aMmN0omQ1K-AEvsBtYnm9jBHiZ_IJJWyJ5sHJ6DJujV_amAhJt9padgVxnkhg4Z5VWgxy2zASXfDKjo_yEzqkxxalnksQNfLfrKYuatbM2_x3iz1Jk0TkSnG5D0ACQDXUmQW2lL-oDHC6TB50r8h5FODc_YXmJaTFXsdIb9hKPKpgmFJ9k4w4jHvD_csr2TfiwUWgvoj-msOMdK5MkMg4lxpmyitFUt7Rxg0RMmpDOZqmKor9CbDOGcS5K1Gj7T445zzFOBllsUDD5GBDMHKgoZfsktX9KlfDgBYg2OyihxxgBxHCE3L3jaahdxMmKUycXjiDKs_bpgQKsOnHuOv-svjS10jc87YgSelR7rokAYw0lxh8EddGxDWi9xp0BvGlH-vi2w5iZ2DrQ2G7_VzYejc62M401gd8PxXe6vL9WrQFj3XsyVB0pPIAi68nUHKQ7DWFCDmeQPUmuUNGHSC6T5BmaB5N8MN4scHWHuD9dtyNLioQtyHmGJmQMNOH6EFnaGUVGnc0f1kb8dd2U7domagVtE4wUqkFzQ0cJIz0AuxIDqqZpHjMHRpFAqxe2HVCl7aybs3ahR3Zsd_vi56b83vZic7zq5ULy-9S6oDgkB4NHHWytQt7-HkEVKVrsZCzdFjOa5pecAWln6jEJQhTJoh-qeQaQ4WeLNMfNTwELUi83OMQn7n-hhQp1uCP1-Q8VH_mikzajsAs58BG-8EaQliV6mEomq8cX2cDyhQp1VKz6llMeY-BQzLqAjGmYwHZJ8EBZWGGlrEUwAPrdz_9Ybb"}, {"type": "function_call", "name": "semantic_search_wikipedia", "arguments": "{\"query\":\"Australian raven adaptations to urban environments behavior diet nesting cities human presence\"}", "call_id": "call_CYHCY65pl37MdkBkDceiC0jl", "id": "fc_0618e42c8eb6e5e4006ab48840272c87d2a19653a6d95eff40", "index": 1}]
-{"name": "semantic_search_wikipedia", "args": {"query": "Australian raven adaptations to urban environments behavior diet nesting cities human presence"}, "id": "call_CYHCY65pl37MdkBkDceiC0jl", "type": "tool_call"}</t>
+    <t>[{"id": "rs_0e88ed93e3722a5e006ab5a38a6eb087d28429b184b486aba1", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtaOK0igmqIgFiYeJ1izBtrvVyv5Tea1WguTRHEgjWJuyo-DyBzXieNtbCHoEVaUrpXNXOCvlkja4-nOESC7TwgD3Uhd0rtCLHn42LjXMYi_gWiG3ipO9DaugbYo69zfG3PswJaaqJ0C4J8zOwr9_o5ivL4jBxZqbSIEe9qRtXXlo1_BTDO_srl-jkaKYtz5vKpcVdR_eoTp0fmQgeTL7XBuaD_atMdNyfKl2ol5UOnwQZsw3qVD0n1SVSDeAxb_D2W3bQ9ihD3jIl4-3PVybDJgkHQux1T094NCTaB0cqu-CKD4DsUaekK6xBicjZo6IVdofhY248BBSahBcGH4Em6_uweFufo5jISsgyvZaiYydvaS5eAtb5HYarHp72MCuzYDUY4MIPMnQC2b6hkY9lhxSqneIHWH-YeTrdTO7ceEdJgAoVtVwGCbI_aVOvlxqHvQIw8HyqaEH7nWnn_fSm7K7GIs8LHTSS8YQ5j0EnFrMlEBfRtzAaP-baJIfDjz8lagPah-H_ez_7SNEcQZ2BVZnlWzEQ3PfqvViso4WicEwam4pvLUls0XjvUAtoW6lBsM3ie4ZNwXlJY2T9oLuUVF8QrIomwgXoApOzA3lcpMG_wUhSW1ePNd3fJEXzwA3DWdcOtcLARhtRM6COultQ1x4jkjOC8tvaj0u7eX6lKr1gkm4W6RRkI4z3yT5XVkvWcUu66nEMdpsl9gdQUT5Irov_Ujq-cPU-_cFRUpk_n49B_OWQ4Sb92-Qn-wDTqtcduPtWoNAyEcmgyfCx0P40IEZfTauD84qmnwIVCN92xdfRgN3TJkENnJvna6NSc1sHxx6JNop6LZxpmEHQLBbGrdd9VsZ7QMbvMttS4T9Wf6NJE_VNHUzTLNxHKPpN_v1F9t9Hb_cW8tnAtMSKCnKJmwau3hwdjQsvd15dpeEJl1g7X52seLwFngUobDJIr14-quOvvIjyUd6gYDLNLLxJjNnIphvNq4qTp22W47-SAE8V49pFguQ7GXV_1_lJkHhzFtojt0HEcqytEDLX4GUAAmxUrGAEBoREJG-z_x-jcoskytFlMX6Z4DAZAWGxnJBu_duLUw_rEDDMIQ2HCpczsCNTOc0-ulx908Khjps-AmLJKw1dqgRqp1Wp9EJ2vSdU5ZB4tFQo7AUq0MkccNPotNes-51JCkx5yZbkV-MGe3WDj6IKBM7wT8pw-dCmInKuf3o"}, {"type": "function_call", "name": "semantic_search_wikipedia", "arguments": "{\"query\":\"Australian raven adaptations to urban environments behavior diet nesting human-modified habitats\"}", "call_id": "call_8utElhKcbeH3BWeuV0h8fYZX", "id": "fc_0e88ed93e3722a5e006ab5a38a964087d28a34f35b39f09885", "index": 1}]
+{"name": "semantic_search_wikipedia", "args": {"query": "Australian raven adaptations to urban environments behavior diet nesting human-modified habitats"}, "id": "call_8utElhKcbeH3BWeuV0h8fYZX", "type": "tool_call"}</t>
   </si>
   <si>
     <t>Call total</t>
@@ -358,25 +358,25 @@
     <t>Tool · semantic_search_wikipedia</t>
   </si>
   <si>
-    <t>01a0d134-3ccb-7261-b0ac-00b3d37b602b</t>
+    <t>01a0d586-d6ff-7170-aa8a-6f1336001102</t>
   </si>
   <si>
     <t xml:space="preserve">    Arguments</t>
   </si>
   <si>
-    <t>{'query': 'Australian raven adaptations to urban environments behavior diet nesting cities human presence'}</t>
+    <t>{'query': 'Australian raven adaptations to urban environments behavior diet nesting human-modified habitats'}</t>
   </si>
   <si>
     <t xml:space="preserve">    Result</t>
   </si>
   <si>
-    <t>{"passages": [{"id": "passage-00016828", "text": "1827, its species name highlighting its similarity with the carrion crow ( c. corone ). two subspecies are recognised, which differ slightly in calls and are quite divergent genetically. the preferred habitat is open woodland and transitional zones. it has adapted well to urban environments and is a common city bird in sydney, canberra and perth. an omnivorous and opportunistic feeder, it eats a wide variety of plant and animal material, as well as food waste from urban areas. in eastern australia its range is strongly correlated with the presence of sheep, and it has been blamed for killing lambs. however, this is very rare, and the raven most often scavenges for afterbirth and stillborn animals as well as newborn lamb faeces. the australian raven is territorial, with pairs generally bonding for life. breeding takes place between july and september, with almost no variation across its range. the nest is a bowl @ - @ shaped structure of sticks sited high in a tree, or occasionally in a man @ - @ made structure such as a windmill or other building. = =", "title": "Australian raven", "license": "CC-BY-SA-3.0", "source_row": 49964, "token_end": 408, "source": "https://huggingface.co/datasets/Salesforce/wikitext/tree/b08601e04326c79dfdd32d625aee71d232d685c3/wikitext-103-raw-v1", "token_start": 188, "cosine_distance": 0.29102271795272827}, {"id": "passage-00016845", "text": "distinguishing australian corvids has hampered understanding of seasonal movements. the australian raven is thought to be largely sedentary, with most movement of over 16 km ( 9 @. @ 9 mi ) due to flocks of non @ - @ breeding subadult birds. juvenile birds leave their parents and join flocks when they are four or five months old. smaller flocks of 8 \u2013 30 birds stay within an area of around 260 square kilometres, while larger flocks of up to 300 birds may travel hundreds of kilometres seeking food. a single breeding pair and their brood can occupy a territory of up to around 120 hectares ( 300 acres ) and remains there year @ - @ round, though groups of ravens may enter this area to forage. australian ravens will defend their territory by chasing, dive @ - @ bombing and occasionally striking the backs of birds of prey, foxes or even people. they generally mate for life, though occasionally one male has been found to be mated with two females in adjacent territories. if the female dies, the male australian raven maintains the territory and finds another mate, while", "token_end": 3604, "source": "https://huggingface.co/datasets/Salesforce/wikitext/tree/b08601e04326c79dfdd32d625aee71d232d685c3/wikitext-103-raw-v1", "license": "CC-BY-SA-3.0", "token_start": 3384, "source_row": 49964, "title": "Australian raven", "cosine_distance": 0.34274810552597046}, {"id": "passage-00016848", "text": "##worms are rarely eaten. australian ravens have been reported killing birds of such size as young galahs ( eolophus roseicapillus ) and starlings ( sturnus vulgaris ). most mammals are eaten as carrion, as many species are too large for the raven to kill, though young rabbits are a frequent prey item. australian ravens drink water frequently, up to ten times a day in hot weather. birds have been observed dunking pieces of meat in water before eating them, as well as doing the same with hard biscuits to make them soggy and soft. australian ravens are intelligent birds, and like many other corvids have innovative methods of seeking out food. foraging takes place in the early morning or late afternoon ; birds rest in the hotter part of the day. food is taken mainly from the ground, birds either finding objects while flying overhead, or by walking along and looking. however, they occasionally feed in trees \u2014 australian ravens forage eucalypt foliage for christmas beetles ( anoplognathus ), and devote a substantial amount of time to look", "source": "https://huggingface.co/datasets/Salesforce/wikitext/tree/b08601e04326c79dfdd32d625aee71d232d685c3/wikitext-103-raw-v1", "license": "CC-BY-SA-3.0", "token_end": 4168, "source_row": 49964, "token_start": 3948, "title": "Australian raven", "cosine_distance": 0.3451145887374878}, {"id": "passage-00016847", "text": "neck. this takes place particularly in autumn, winter and spring, and is important in pair bonding. either member may initiate it, generally by landing near the other bird, shuffling next to its mate, then bending its head forward and presenting its nape. = = = feeding = = = the australian raven is omnivorous, though eats more meat than smaller corvids. its diet in summer contains a high proportion of insects, while more plant items are eaten in autumn. flesh makes up over half its diet in winter. invertebrates commonly eaten include spiders, millipedes, centipedes ( which ravens behead before eating ), grasshoppers, cicadas and caterpillars ( especially of the family noctuidae ), which are important in feeding nestlings. australian ravens sometimes eat yabbies ( cherax destructor ) from the edges of dams. unusually for a ground @ - @ feeding omnivore, earthworms are rarely eaten. australian ravens have been reported killing birds of such size as young galahs ( eolophus roseicapillus ) and starlings", "source_row": 49964, "title": "Australian raven", "license": "CC-BY-SA-3.0", "token_start": 3760, "token_end": 3980, "source": "https://huggingface.co/datasets/Salesforce/wikitext/tree/b08601e04326c79dfdd32d625aee71d232d685c3/wikitext-103-raw-v1", "cosine_distance": 0.36243724822998047}], "note": "Nearest passages are candidates, not proof of relevance; abstain if they do not answer the question."}</t>
+    <t>{"passages": [{"id": "passage-00016828", "text": "1827, its species name highlighting its similarity with the carrion crow ( c. corone ). two subspecies are recognised, which differ slightly in calls and are quite divergent genetically. the preferred habitat is open woodland and transitional zones. it has adapted well to urban environments and is a common city bird in sydney, canberra and perth. an omnivorous and opportunistic feeder, it eats a wide variety of plant and animal material, as well as food waste from urban areas. in eastern australia its range is strongly correlated with the presence of sheep, and it has been blamed for killing lambs. however, this is very rare, and the raven most often scavenges for afterbirth and stillborn animals as well as newborn lamb faeces. the australian raven is territorial, with pairs generally bonding for life. breeding takes place between july and september, with almost no variation across its range. the nest is a bowl @ - @ shaped structure of sticks sited high in a tree, or occasionally in a man @ - @ made structure such as a windmill or other building. = =", "token_start": 188, "title": "Australian raven", "source": "https://huggingface.co/datasets/Salesforce/wikitext/tree/b08601e04326c79dfdd32d625aee71d232d685c3/wikitext-103-raw-v1", "token_end": 408, "source_row": 49964, "license": "CC-BY-SA-3.0", "cosine_distance": 0.2578777074813843}, {"id": "passage-00016847", "text": "neck. this takes place particularly in autumn, winter and spring, and is important in pair bonding. either member may initiate it, generally by landing near the other bird, shuffling next to its mate, then bending its head forward and presenting its nape. = = = feeding = = = the australian raven is omnivorous, though eats more meat than smaller corvids. its diet in summer contains a high proportion of insects, while more plant items are eaten in autumn. flesh makes up over half its diet in winter. invertebrates commonly eaten include spiders, millipedes, centipedes ( which ravens behead before eating ), grasshoppers, cicadas and caterpillars ( especially of the family noctuidae ), which are important in feeding nestlings. australian ravens sometimes eat yabbies ( cherax destructor ) from the edges of dams. unusually for a ground @ - @ feeding omnivore, earthworms are rarely eaten. australian ravens have been reported killing birds of such size as young galahs ( eolophus roseicapillus ) and starlings", "token_start": 3760, "token_end": 3980, "source_row": 49964, "source": "https://huggingface.co/datasets/Salesforce/wikitext/tree/b08601e04326c79dfdd32d625aee71d232d685c3/wikitext-103-raw-v1", "title": "Australian raven", "license": "CC-BY-SA-3.0", "cosine_distance": 0.29934078454971313}, {"id": "passage-00016848", "text": "##worms are rarely eaten. australian ravens have been reported killing birds of such size as young galahs ( eolophus roseicapillus ) and starlings ( sturnus vulgaris ). most mammals are eaten as carrion, as many species are too large for the raven to kill, though young rabbits are a frequent prey item. australian ravens drink water frequently, up to ten times a day in hot weather. birds have been observed dunking pieces of meat in water before eating them, as well as doing the same with hard biscuits to make them soggy and soft. australian ravens are intelligent birds, and like many other corvids have innovative methods of seeking out food. foraging takes place in the early morning or late afternoon ; birds rest in the hotter part of the day. food is taken mainly from the ground, birds either finding objects while flying overhead, or by walking along and looking. however, they occasionally feed in trees \u2014 australian ravens forage eucalypt foliage for christmas beetles ( anoplognathus ), and devote a substantial amount of time to look", "source": "https://huggingface.co/datasets/Salesforce/wikitext/tree/b08601e04326c79dfdd32d625aee71d232d685c3/wikitext-103-raw-v1", "token_start": 3948, "token_end": 4168, "source_row": 49964, "title": "Australian raven", "license": "CC-BY-SA-3.0", "cosine_distance": 0.30970287322998047}, {"id": "passage-00016845", "text": "distinguishing australian corvids has hampered understanding of seasonal movements. the australian raven is thought to be largely sedentary, with most movement of over 16 km ( 9 @. @ 9 mi ) due to flocks of non @ - @ breeding subadult birds. juvenile birds leave their parents and join flocks when they are four or five months old. smaller flocks of 8 \u2013 30 birds stay within an area of around 260 square kilometres, while larger flocks of up to 300 birds may travel hundreds of kilometres seeking food. a single breeding pair and their brood can occupy a territory of up to around 120 hectares ( 300 acres ) and remains there year @ - @ round, though groups of ravens may enter this area to forage. australian ravens will defend their territory by chasing, dive @ - @ bombing and occasionally striking the backs of birds of prey, foxes or even people. they generally mate for life, though occasionally one male has been found to be mated with two females in adjacent territories. if the female dies, the male australian raven maintains the territory and finds another mate, while", "license": "CC-BY-SA-3.0", "source": "https://huggingface.co/datasets/Salesforce/wikitext/tree/b08601e04326c79dfdd32d625aee71d232d685c3/wikitext-103-raw-v1", "source_row": 49964, "token_end": 3604, "token_start": 3384, "title": "Australian raven", "cosine_distance": 0.3153247833251953}], "note": "Nearest passages are candidates, not proof of relevance; abstain if they do not answer the question."}</t>
   </si>
   <si>
     <t>R2</t>
   </si>
   <si>
-    <t>01a0d134-3dd3-7be1-9a07-6c076d5c73bf</t>
+    <t>01a0d586-d816-7e30-bace-67bf587eb376</t>
   </si>
   <si>
     <t>Conversation history · cache read</t>
@@ -385,7 +385,7 @@
     <t xml:space="preserve">    Tool result</t>
   </si>
   <si>
-    <t>[{"type": "text", "text": "The Australian raven has adapted to urban environments in several ways:\n\n- **Flexible diet:** It is an opportunistic omnivore, eating varied plant and animal matter as well as **food waste** from urban areas. [passage-00016828]\n- **Use of human structures:** Although it usually nests high in trees, it may also build nests on **man-made structures**, including windmills and other buildings. [passage-00016828]\n- **Behavioral flexibility:** Its intelligence and innovative foraging methods help it locate and exploit new food sources. [passage-00016848]\n- **Urban tolerance:** These adaptations have enabled it to become a common city bird in **Sydney, Canberra, and Perth**. [passage-00016828]\n\nThe indexed passages support these adaptations, but do not provide detailed evidence about other possible urban changes, such as altered calls, traffic avoidance, or changes in breeding success.", "phase": "final_answer", "index": 0, "id": "msg_0618e42c8eb6e5e4006ab48841b11487d2b4ee50c8bb0eb34f"}]</t>
+    <t>[{"id": "rs_0e88ed93e3722a5e006ab5a38c0dec87d2a1da1a04f5ce7006", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtaOMypnI2WvnpoaqSo_hq1IA642sVlLVlIwLc3j-9hdiat4FuCxIRlG2gUV9WG0EcVQCdAx8Wza8HUZASc_PIL9_ZnU0w_reunAAou20TQPDn9BcZ21Ji6n79t9PoaQEQbFBZUkVexyuJ34QL4p-Tvg9ethxhpfQCtmAQwpn5nFKaLHb3kYhxhzWhjgq7m5xCXc26C3zjXY_-BqRrIWfSn-YGCdWP8TVaq-GKlwek93RgFO7rB76ZfnqBCbL2kd2SevGarAsk0dUKDC0sh3Q9bzscrPlQOTuB5uMj1IKHr3qXKY7-WJ0KIphyFarl9H-NwbcLTYULu63w9jtVQ_xP25LTohJO4hBxOqFXOJLwIvahET8lVmDGJfkLEDQ9FklyyojgWKmBhBIwK4edg1fYkfmlYZpZ0mQMnu011tWc8wE0wVwilwhW-0ls7MuQe5n5lHa7B8uA69ZKAQkE-9_J_EVngqom6yp4l2EsrTUfIyrIxMgdbDRKKKd3VBY56rOzqaXUOn_XP5s_KsQeV18wQuR2PLUfz5PttbqpkSY3L5BHSgf0hC1XmT2VnSQ_ryiWjS-b-LwOEEAeI6rM6ay0BXZFHxs4F4AnTtFeJwEOku-2gXAUwaM21SMOLj62SN8BrmoH0IS6dujYqE437YeK3N8rjNWfFucWWgZSM-caLFqqBMHazvlGa0Lw6Kdjs-huBddH0SXQfKhD8NGOpe3Kj_0cwga0zM7GULli32WfjygcqBCX2pj_4bhljPFA7UUe3_8Jc4XvGJR3hdZCdnslcbnEUiYKa14EsTtHAM5j4FXns12KqWRIixZ928-rKmFH6l1pY2bGRKoSMNYa1EKFsYa18Xdb8ZCDuCk3AVGVbokX9s98Io4PFVVHe7ISfh79imefXWm4HlHES0jPrMENk5541S-1qx0qc31lbOvDdS3mevMKZxTz8umH0CYjqH2iKYemrqAxllwIZMC-78uMMxg_XzaiRprJuxQB1x2ArFT_iH8gBaTu2sCf37yYIKz0GhayjO3nfKrUayHelWDu_O283KYY84g-smA-zEVaxJvL6EXEO6iI7N8I-6c30hAkkVKm8kmqf0bjnJNNI1WAXyCcHvG_dwjG2gNM-UmaF1Ti3_rmWga2frY0gr5kcRMz5qO80SUi7IVC-wlBe56cC61swlXWufi8VXR779cuJSb--jkaqzIhS6zQYvLzoIyXJ1gKqRZyX7mc0wbRgRLarloU35862fCDu_R0qOOdn8ATJ5F2l3KCsBQ5-3k4brOXBbArTQ71CbCZ4EvwtUjWgJaFUHfMTCFSoj3DSBO2KeqFL31Zxz1N0Yp-px_ReTVfpnZ-Jx1pxgKv10j4DkP72yuqth1lpWoQl8pJV_EsoOQVUCrALFtFLhNOBfVfHjkkZlmJMQFEaygsMum_4xvYfaFLoX3NTjIkKWJZa2vP6P5qF06rb3pvNWr6CSF3R2169WSGEbdm2NIJd9f6ci0my9ZFxaqFt5F7IzmwDTtvGVxCXcw4EdmGNGrwWhIdsTRM1hkauH_Xj3RJGfVtAtglW7fzw=="}, {"type": "text", "text": "The Australian raven has adapted to cities in several ways:\n\n- **Flexible habitat use:** It can live in urban areas and is common in cities such as Sydney, Canberra, and Perth. [passage-00016828]\n- **Opportunistic feeding:** As an omnivore, it eats varied plant and animal foods, including **urban food waste** and carrion. [passage-00016828]\n- **Use of artificial structures:** Although it usually nests high in trees, it may also nest on human-made structures such as buildings and windmills. [passage-00016828]\n- **Behavioral flexibility:** Its intelligence and innovative foraging methods help it locate and handle different food sources. [passage-00016848]\n\nThe indexed Wikipedia passages support these adaptations, but do not provide detailed evidence about specific urban pressures\u2014such as traffic, artificial light, or human disturbance.", "phase": "final_answer", "index": 1, "id": "msg_0e88ed93e3722a5e006ab5a38c7e1487d2baaa5de9b1121a10"}]</t>
   </si>
   <si>
     <t>wikipedia_rag_agent</t>
@@ -406,7 +406,7 @@
     <t>Prepare the current conversation, run model middleware, and invoke the chat model.</t>
   </si>
   <si>
-    <t>01a0d134-3662-7413-acc6-513f2ab0a705</t>
+    <t>01a0d586-d0bc-7be1-a7cd-9bfc6fb6a24a</t>
   </si>
   <si>
     <t xml:space="preserve">        ChatOpenAI</t>
@@ -427,7 +427,7 @@
     <t>Execute tool calls requested by the preceding model response and return their observations.</t>
   </si>
   <si>
-    <t>01a0d134-3cca-7f33-ac39-c5e3e40bd955</t>
+    <t>01a0d586-d6fe-7520-ae45-bbed177a537c</t>
   </si>
   <si>
     <t>No model charge</t>
@@ -443,7 +443,7 @@
 passages are candidates; check relevance before using them as evidence.</t>
   </si>
   <si>
-    <t>01a0d134-3dd2-7d90-8469-48a08bc204e1</t>
+    <t>01a0d586-d815-7322-8024-840807910c4e</t>
   </si>
 </sst>
 </file>
@@ -850,7 +850,7 @@
   <sheetPr>
     <tabColor rgb="FF173B70"/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -910,20 +910,20 @@
         <v>91</v>
       </c>
       <c r="E2" s="2">
-        <f>IF(COUNT('Turns'!E17,'Turns'!E32)=2,SUM('Turns'!E17,'Turns'!E32),"Unknown")</f>
-        <v>0.0006467024825</v>
+        <f>IF(COUNT('Turns'!E17,'Turns'!E33)=2,SUM('Turns'!E17,'Turns'!E33),"Unknown")</f>
+        <v>0.000708542596</v>
       </c>
       <c r="F2" s="2">
-        <f>IF(COUNT('Turns'!F17,'Turns'!F32)=2,SUM('Turns'!F17,'Turns'!F32),"Unknown")</f>
-        <v>0.00073795</v>
+        <f>IF(COUNT('Turns'!F17,'Turns'!F33)=2,SUM('Turns'!F17,'Turns'!F33),"Unknown")</f>
+        <v>0.0008054</v>
       </c>
       <c r="G2" s="5">
         <f>IF(ISNUMBER(E2),ROUND(E2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>65.0</v>
+        <v>71.0</v>
       </c>
       <c r="H2" s="5">
         <f>IF(ISNUMBER(F2),ROUND(F2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>74.0</v>
+        <v>81.0</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -934,20 +934,20 @@
         <v>92</v>
       </c>
       <c r="E3" s="2">
-        <f>IF(COUNT('Turns'!E17,'Turns'!E32)=2,SUM('Turns'!E17,'Turns'!E32),"Unknown")</f>
-        <v>0.0006467024825</v>
+        <f>IF(COUNT('Turns'!E17,'Turns'!E33)=2,SUM('Turns'!E17,'Turns'!E33),"Unknown")</f>
+        <v>0.000708542596</v>
       </c>
       <c r="F3" s="2">
-        <f>IF(COUNT('Turns'!F17,'Turns'!F32)=2,SUM('Turns'!F17,'Turns'!F32),"Unknown")</f>
-        <v>0.00073795</v>
+        <f>IF(COUNT('Turns'!F17,'Turns'!F33)=2,SUM('Turns'!F17,'Turns'!F33),"Unknown")</f>
+        <v>0.0008054</v>
       </c>
       <c r="G3" s="5">
         <f>IF(ISNUMBER(E3),ROUND(E3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>65.0</v>
+        <v>71.0</v>
       </c>
       <c r="H3" s="5">
         <f>IF(ISNUMBER(F3),ROUND(F3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>74.0</v>
+        <v>81.0</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -985,7 +985,7 @@
       </c>
       <c r="E5" s="2">
         <f>IF(AND(ISNUMBER(F5),ISNUMBER('Reference data'!$B$3)),F5*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.312603e-05</v>
+        <v>3.3254172e-05</v>
       </c>
       <c r="F5" s="2">
         <f>IF(D5=0,0,IF(ISNUMBER('Reference data'!B17),D5*'Reference data'!B17/1000000,"Unknown"))</f>
@@ -1072,7 +1072,7 @@
         <v>105</v>
       </c>
       <c r="D11" s="4">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="24" customHeight="1">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="E12" s="2">
         <f>IF(AND(ISNUMBER(F12),ISNUMBER('Reference data'!$B$3)),F12*'Reference data'!$B$3,"Unknown")</f>
-        <v>9.46458e-06</v>
+        <v>9.501192e-06</v>
       </c>
       <c r="F12" s="2">
         <f>IF(D12=0,0,IF(ISNUMBER('Reference data'!F17),D12*'Reference data'!F17/1000000,"Unknown"))</f>
@@ -1116,19 +1116,19 @@
         <v>107</v>
       </c>
       <c r="D13" s="5">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E13" s="2">
         <f>IF(AND(ISNUMBER(F13),ISNUMBER('Reference data'!$B$3)),F13*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.470346e-05</v>
+        <v>3.5893392e-05</v>
       </c>
       <c r="F13" s="2">
         <f>IF(D13=0,0,IF(ISNUMBER('Reference data'!E17),D13*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>3.96e-05</v>
+        <v>4.08e-05</v>
       </c>
       <c r="G13" s="5">
         <f>IF(ISNUMBER(E13),ROUND(E13*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="H13" s="5">
         <f>IF(ISNUMBER(F13),ROUND(F13*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1183,11 +1183,11 @@
       </c>
       <c r="E17" s="2">
         <f>IF(COUNT('Turns'!E5,'Turns'!E12,'Turns'!E13)=3,SUM('Turns'!E5,'Turns'!E12,'Turns'!E13),"Unknown")</f>
-        <v>7.729407e-05</v>
+        <v>7.8648756e-05</v>
       </c>
       <c r="F17" s="2">
         <f>IF(COUNT('Turns'!F5,'Turns'!F12,'Turns'!F13)=3,SUM('Turns'!F5,'Turns'!F12,'Turns'!F13),"Unknown")</f>
-        <v>8.82e-05</v>
+        <v>8.94e-05</v>
       </c>
       <c r="G17" s="5">
         <f>IF(ISNUMBER(E17),ROUND(E17*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1248,7 +1248,7 @@
         <v>94</v>
       </c>
       <c r="D21" s="4">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>95</v>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="E23" s="2">
         <f>IF(AND(ISNUMBER(F23),ISNUMBER('Reference data'!$B$3)),F23*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.2581e-07</v>
+        <v>5.27844e-07</v>
       </c>
       <c r="F23" s="2">
         <f>IF(D23=0,0,IF(ISNUMBER('Reference data'!B17),D23*'Reference data'!B17/1000000,"Unknown"))</f>
@@ -1342,15 +1342,15 @@
         <v>103</v>
       </c>
       <c r="D25" s="5">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="E25" s="2">
         <f>IF(AND(ISNUMBER(F25),ISNUMBER('Reference data'!$B$3)),F25*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.0003669715625</v>
+        <v>0.00036861106</v>
       </c>
       <c r="F25" s="2">
         <f>IF(D25=0,0,IF(ISNUMBER('Reference data'!D17),D25*'Reference data'!D17/1000000,"Unknown"))</f>
-        <v>0.00041875</v>
+        <v>0.000419</v>
       </c>
       <c r="G25" s="5">
         <f>IF(ISNUMBER(E25),ROUND(E25*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1383,7 +1383,7 @@
         <v>105</v>
       </c>
       <c r="D27" s="4">
-        <v>192</v>
+        <v>247</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="24" customHeight="1">
@@ -1394,29 +1394,29 @@
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D28" s="5">
-        <v>192</v>
+        <v>60</v>
       </c>
       <c r="E28" s="2">
         <f>IF(AND(ISNUMBER(F28),ISNUMBER('Reference data'!$B$3)),F28*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.00020191104</v>
+        <v>6.334128e-05</v>
       </c>
       <c r="F28" s="2">
-        <f>IF(D28=0,0,IF(ISNUMBER('Reference data'!E17),D28*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>0.0002304</v>
+        <f>IF(D28=0,0,IF(ISNUMBER('Reference data'!F17),D28*'Reference data'!F17/1000000,"Unknown"))</f>
+        <v>7.2e-05</v>
       </c>
       <c r="G28" s="5">
         <f>IF(ISNUMBER(E28),ROUND(E28*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>20.0</v>
+        <v>6.0</v>
       </c>
       <c r="H28" s="5">
         <f>IF(ISNUMBER(F28),ROUND(F28*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>23.0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="164" customHeight="1">
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="24" customHeight="1">
       <c r="A29" t="s">
         <v>118</v>
       </c>
@@ -1424,13 +1424,29 @@
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>108</v>
-      </c>
-      <c r="I29" s="6" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="24" customHeight="1">
+        <v>107</v>
+      </c>
+      <c r="D29" s="5">
+        <v>187</v>
+      </c>
+      <c r="E29" s="2">
+        <f>IF(AND(ISNUMBER(F29),ISNUMBER('Reference data'!$B$3)),F29*'Reference data'!$B$3,"Unknown")</f>
+        <v>0.000197413656</v>
+      </c>
+      <c r="F29" s="2">
+        <f>IF(D29=0,0,IF(ISNUMBER('Reference data'!E17),D29*'Reference data'!E17/1000000,"Unknown"))</f>
+        <v>0.0002244</v>
+      </c>
+      <c r="G29" s="5">
+        <f>IF(ISNUMBER(E29),ROUND(E29*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>20.0</v>
+      </c>
+      <c r="H29" s="5">
+        <f>IF(ISNUMBER(F29),ROUND(F29*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>22.0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="409" customHeight="1">
       <c r="A30" t="s">
         <v>118</v>
       </c>
@@ -1438,7 +1454,10 @@
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>103</v>
+        <v>108</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="24" customHeight="1">
@@ -1449,41 +1468,52 @@
         <v>1</v>
       </c>
       <c r="C31" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="24" customHeight="1">
+      <c r="A32" t="s">
+        <v>118</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="32" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
-      <c r="A32" s="4" t="s">
+    <row r="33" spans="1:11" s="4" customFormat="1" ht="24" customHeight="1">
+      <c r="A33" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="B32" s="4">
-        <v>1</v>
-      </c>
-      <c r="C32" s="4" t="s">
+      <c r="B33" s="4">
+        <v>1</v>
+      </c>
+      <c r="C33" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="E32" s="2">
-        <f>IF(COUNT('Turns'!E22,'Turns'!E23,'Turns'!E25,'Turns'!E28)=4,SUM('Turns'!E22,'Turns'!E23,'Turns'!E25,'Turns'!E28),"Unknown")</f>
-        <v>0.0005694084125</v>
-      </c>
-      <c r="F32" s="2">
-        <f>IF(COUNT('Turns'!F22,'Turns'!F23,'Turns'!F25,'Turns'!F28)=4,SUM('Turns'!F22,'Turns'!F23,'Turns'!F25,'Turns'!F28),"Unknown")</f>
-        <v>0.00064975</v>
-      </c>
-      <c r="G32" s="5">
-        <f>IF(ISNUMBER(E32),ROUND(E32*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>57.0</v>
-      </c>
-      <c r="H32" s="5">
-        <f>IF(ISNUMBER(F32),ROUND(F32*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>65.0</v>
-      </c>
-      <c r="K32" s="4" t="s">
+      <c r="E33" s="2">
+        <f>IF(COUNT('Turns'!E22,'Turns'!E23,'Turns'!E25,'Turns'!E28,'Turns'!E29)=5,SUM('Turns'!E22,'Turns'!E23,'Turns'!E25,'Turns'!E28,'Turns'!E29),"Unknown")</f>
+        <v>0.00062989384</v>
+      </c>
+      <c r="F33" s="2">
+        <f>IF(COUNT('Turns'!F22,'Turns'!F23,'Turns'!F25,'Turns'!F28,'Turns'!F29)=5,SUM('Turns'!F22,'Turns'!F23,'Turns'!F25,'Turns'!F28,'Turns'!F29),"Unknown")</f>
+        <v>0.000716</v>
+      </c>
+      <c r="G33" s="5">
+        <f>IF(ISNUMBER(E33),ROUND(E33*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>63.0</v>
+      </c>
+      <c r="H33" s="5">
+        <f>IF(ISNUMBER(F33),ROUND(F33*'Reference data'!$B$2,0),"Unknown")</f>
+        <v>72.0</v>
+      </c>
+      <c r="K33" s="4" t="s">
         <v>111</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:AE32">
+  <conditionalFormatting sqref="A2:AE33">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$K2="error"</formula>
     </cfRule>
@@ -1630,7 +1660,7 @@
       </c>
       <c r="K2" s="2">
         <f>IF(COUNT('Turns'!E5,'Turns'!E23)=2,SUM('Turns'!E5,'Turns'!E23),"Unknown")</f>
-        <v>3.365184e-05</v>
+        <v>3.3782016e-05</v>
       </c>
       <c r="L2" s="2">
         <f>IF(COUNT('Turns'!F5,'Turns'!F23)=2,SUM('Turns'!F5,'Turns'!F23),"Unknown")</f>
@@ -1650,58 +1680,58 @@
       </c>
       <c r="P2" s="2">
         <f>IF(COUNT('Turns'!D25)=1,SUM('Turns'!D25),"Unknown")</f>
-        <v>1675.0</v>
+        <v>1676.0</v>
       </c>
       <c r="Q2" s="2">
         <f>IF(COUNT('Turns'!E25)=1,SUM('Turns'!E25),"Unknown")</f>
-        <v>0.0003669715625</v>
+        <v>0.00036861106</v>
       </c>
       <c r="R2" s="2">
         <f>IF(COUNT('Turns'!F25)=1,SUM('Turns'!F25),"Unknown")</f>
-        <v>0.00041875</v>
+        <v>0.000419</v>
       </c>
       <c r="S2" s="2">
-        <f>IF(COUNT('Turns'!D13,'Turns'!D28)=2,SUM('Turns'!D13,'Turns'!D28),"Unknown")</f>
-        <v>225.0</v>
+        <f>IF(COUNT('Turns'!D13,'Turns'!D29)=2,SUM('Turns'!D13,'Turns'!D29),"Unknown")</f>
+        <v>221.0</v>
       </c>
       <c r="T2" s="2">
-        <f>IF(COUNT('Turns'!E13,'Turns'!E28)=2,SUM('Turns'!E13,'Turns'!E28),"Unknown")</f>
-        <v>0.0002366145</v>
+        <f>IF(COUNT('Turns'!E13,'Turns'!E29)=2,SUM('Turns'!E13,'Turns'!E29),"Unknown")</f>
+        <v>0.000233307048</v>
       </c>
       <c r="U2" s="2">
-        <f>IF(COUNT('Turns'!F13,'Turns'!F28)=2,SUM('Turns'!F13,'Turns'!F28),"Unknown")</f>
-        <v>0.00027</v>
+        <f>IF(COUNT('Turns'!F13,'Turns'!F29)=2,SUM('Turns'!F13,'Turns'!F29),"Unknown")</f>
+        <v>0.0002652</v>
       </c>
       <c r="V2" s="2">
-        <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
-        <v>9.0</v>
+        <f>IF(COUNT('Turns'!D12,'Turns'!D28)=2,SUM('Turns'!D12,'Turns'!D28),"Unknown")</f>
+        <v>69.0</v>
       </c>
       <c r="W2" s="2">
-        <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>9.46458e-06</v>
+        <f>IF(COUNT('Turns'!E12,'Turns'!E28)=2,SUM('Turns'!E12,'Turns'!E28),"Unknown")</f>
+        <v>7.2842472e-05</v>
       </c>
       <c r="X2" s="2">
-        <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
-        <v>1.08e-05</v>
+        <f>IF(COUNT('Turns'!F12,'Turns'!F28)=2,SUM('Turns'!F12,'Turns'!F28),"Unknown")</f>
+        <v>8.28e-05</v>
       </c>
       <c r="Y2" s="2">
-        <f>IF(COUNT('Turns'!E17,'Turns'!E32)=2,SUM('Turns'!E17,'Turns'!E32),"Unknown")</f>
-        <v>0.0006467024825</v>
+        <f>IF(COUNT('Turns'!E17,'Turns'!E33)=2,SUM('Turns'!E17,'Turns'!E33),"Unknown")</f>
+        <v>0.000708542596</v>
       </c>
       <c r="Z2" s="2">
-        <f>IF(COUNT('Turns'!F17,'Turns'!F32)=2,SUM('Turns'!F17,'Turns'!F32),"Unknown")</f>
-        <v>0.00073795</v>
+        <f>IF(COUNT('Turns'!F17,'Turns'!F33)=2,SUM('Turns'!F17,'Turns'!F33),"Unknown")</f>
+        <v>0.0008054</v>
       </c>
       <c r="AA2" s="5">
         <f>IF(ISNUMBER(Y2),ROUND(Y2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>65.0</v>
+        <v>71.0</v>
       </c>
       <c r="AB2" s="5">
         <f>IF(ISNUMBER(Z2),ROUND(Z2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>74.0</v>
+        <v>81.0</v>
       </c>
       <c r="AD2" s="1">
-        <v>5029.036</v>
+        <v>4354.374</v>
       </c>
       <c r="AE2" s="1" t="s">
         <v>126</v>
@@ -1738,7 +1768,7 @@
       </c>
       <c r="K3" s="2">
         <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>3.312603e-05</v>
+        <v>3.3254172e-05</v>
       </c>
       <c r="L3" s="2">
         <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
@@ -1764,15 +1794,15 @@
       </c>
       <c r="S3" s="2">
         <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
       <c r="T3" s="2">
         <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>3.470346e-05</v>
+        <v>3.5893392e-05</v>
       </c>
       <c r="U3" s="2">
         <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
-        <v>3.96e-05</v>
+        <v>4.08e-05</v>
       </c>
       <c r="V3" s="2">
         <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
@@ -1780,7 +1810,7 @@
       </c>
       <c r="W3" s="2">
         <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>9.46458e-06</v>
+        <v>9.501192e-06</v>
       </c>
       <c r="X3" s="2">
         <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
@@ -1788,11 +1818,11 @@
       </c>
       <c r="Y3" s="2">
         <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>7.729407e-05</v>
+        <v>7.8648756e-05</v>
       </c>
       <c r="Z3" s="2">
         <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>8.82e-05</v>
+        <v>8.94e-05</v>
       </c>
       <c r="AA3" s="5">
         <f>IF(ISNUMBER(Y3),ROUND(Y3*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1803,7 +1833,7 @@
         <v>9.0</v>
       </c>
       <c r="AD3" s="1">
-        <v>1639.068</v>
+        <v>1600.472</v>
       </c>
       <c r="AE3" s="1" t="s">
         <v>126</v>
@@ -1843,7 +1873,7 @@
       </c>
       <c r="K4" s="2">
         <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>3.312603e-05</v>
+        <v>3.3254172e-05</v>
       </c>
       <c r="L4" s="2">
         <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
@@ -1869,15 +1899,15 @@
       </c>
       <c r="S4" s="2">
         <f>IF(COUNT('Turns'!D13)=1,SUM('Turns'!D13),"Unknown")</f>
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
       <c r="T4" s="2">
         <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>3.470346e-05</v>
+        <v>3.5893392e-05</v>
       </c>
       <c r="U4" s="2">
         <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
-        <v>3.96e-05</v>
+        <v>4.08e-05</v>
       </c>
       <c r="V4" s="2">
         <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
@@ -1885,7 +1915,7 @@
       </c>
       <c r="W4" s="2">
         <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>9.46458e-06</v>
+        <v>9.501192e-06</v>
       </c>
       <c r="X4" s="2">
         <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
@@ -1893,11 +1923,11 @@
       </c>
       <c r="Y4" s="2">
         <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>7.729407e-05</v>
+        <v>7.8648756e-05</v>
       </c>
       <c r="Z4" s="2">
         <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>8.82e-05</v>
+        <v>8.94e-05</v>
       </c>
       <c r="AA4" s="5">
         <f>IF(ISNUMBER(Y4),ROUND(Y4*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1911,7 +1941,7 @@
         <v>93</v>
       </c>
       <c r="AD4" s="1">
-        <v>1636.7</v>
+        <v>1598.235</v>
       </c>
       <c r="AE4" s="1" t="s">
         <v>133</v>
@@ -1943,7 +1973,7 @@
         <v>49</v>
       </c>
       <c r="AD5" s="1">
-        <v>262.725</v>
+        <v>277.66</v>
       </c>
       <c r="AE5" s="1" t="s">
         <v>137</v>
@@ -1975,7 +2005,7 @@
         <v>136</v>
       </c>
       <c r="AD6" s="1">
-        <v>260.596</v>
+        <v>274.634</v>
       </c>
       <c r="AE6" s="1" t="s">
         <v>137</v>
@@ -2012,7 +2042,7 @@
       </c>
       <c r="K7" s="2">
         <f>IF(COUNT('Turns'!E23)=1,SUM('Turns'!E23),"Unknown")</f>
-        <v>5.2581e-07</v>
+        <v>5.27844e-07</v>
       </c>
       <c r="L7" s="2">
         <f>IF(COUNT('Turns'!F23)=1,SUM('Turns'!F23),"Unknown")</f>
@@ -2032,55 +2062,58 @@
       </c>
       <c r="P7" s="2">
         <f>IF(COUNT('Turns'!D25)=1,SUM('Turns'!D25),"Unknown")</f>
-        <v>1675.0</v>
+        <v>1676.0</v>
       </c>
       <c r="Q7" s="2">
         <f>IF(COUNT('Turns'!E25)=1,SUM('Turns'!E25),"Unknown")</f>
-        <v>0.0003669715625</v>
+        <v>0.00036861106</v>
       </c>
       <c r="R7" s="2">
         <f>IF(COUNT('Turns'!F25)=1,SUM('Turns'!F25),"Unknown")</f>
-        <v>0.00041875</v>
+        <v>0.000419</v>
       </c>
       <c r="S7" s="2">
+        <f>IF(COUNT('Turns'!D29)=1,SUM('Turns'!D29),"Unknown")</f>
+        <v>187.0</v>
+      </c>
+      <c r="T7" s="2">
+        <f>IF(COUNT('Turns'!E29)=1,SUM('Turns'!E29),"Unknown")</f>
+        <v>0.000197413656</v>
+      </c>
+      <c r="U7" s="2">
+        <f>IF(COUNT('Turns'!F29)=1,SUM('Turns'!F29),"Unknown")</f>
+        <v>0.0002244</v>
+      </c>
+      <c r="V7" s="2">
         <f>IF(COUNT('Turns'!D28)=1,SUM('Turns'!D28),"Unknown")</f>
-        <v>192.0</v>
-      </c>
-      <c r="T7" s="2">
+        <v>60.0</v>
+      </c>
+      <c r="W7" s="2">
         <f>IF(COUNT('Turns'!E28)=1,SUM('Turns'!E28),"Unknown")</f>
-        <v>0.00020191104</v>
-      </c>
-      <c r="U7" s="2">
+        <v>6.334128e-05</v>
+      </c>
+      <c r="X7" s="2">
         <f>IF(COUNT('Turns'!F28)=1,SUM('Turns'!F28),"Unknown")</f>
-        <v>0.0002304</v>
-      </c>
-      <c r="V7" s="2">
-        <v>0</v>
-      </c>
-      <c r="W7" s="2">
-        <v>0</v>
-      </c>
-      <c r="X7" s="2">
-        <v>0</v>
+        <v>7.2e-05</v>
       </c>
       <c r="Y7" s="2">
-        <f>IF(COUNT('Turns'!E32)=1,SUM('Turns'!E32),"Unknown")</f>
-        <v>0.0005694084125</v>
+        <f>IF(COUNT('Turns'!E33)=1,SUM('Turns'!E33),"Unknown")</f>
+        <v>0.00062989384</v>
       </c>
       <c r="Z7" s="2">
-        <f>IF(COUNT('Turns'!F32)=1,SUM('Turns'!F32),"Unknown")</f>
-        <v>0.00064975</v>
+        <f>IF(COUNT('Turns'!F33)=1,SUM('Turns'!F33),"Unknown")</f>
+        <v>0.000716</v>
       </c>
       <c r="AA7" s="5">
         <f>IF(ISNUMBER(Y7),ROUND(Y7*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>57.0</v>
+        <v>63.0</v>
       </c>
       <c r="AB7" s="5">
         <f>IF(ISNUMBER(Z7),ROUND(Z7*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>65.0</v>
+        <v>72.0</v>
       </c>
       <c r="AD7" s="1">
-        <v>3121.866</v>
+        <v>2472.083</v>
       </c>
       <c r="AE7" s="1" t="s">
         <v>126</v>
@@ -2103,7 +2136,7 @@
         <v>111</v>
       </c>
       <c r="F8" s="1">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>132</v>
@@ -2120,7 +2153,7 @@
       </c>
       <c r="K8" s="2">
         <f>IF(COUNT('Turns'!E23)=1,SUM('Turns'!E23),"Unknown")</f>
-        <v>5.2581e-07</v>
+        <v>5.27844e-07</v>
       </c>
       <c r="L8" s="2">
         <f>IF(COUNT('Turns'!F23)=1,SUM('Turns'!F23),"Unknown")</f>
@@ -2140,58 +2173,61 @@
       </c>
       <c r="P8" s="2">
         <f>IF(COUNT('Turns'!D25)=1,SUM('Turns'!D25),"Unknown")</f>
-        <v>1675.0</v>
+        <v>1676.0</v>
       </c>
       <c r="Q8" s="2">
         <f>IF(COUNT('Turns'!E25)=1,SUM('Turns'!E25),"Unknown")</f>
-        <v>0.0003669715625</v>
+        <v>0.00036861106</v>
       </c>
       <c r="R8" s="2">
         <f>IF(COUNT('Turns'!F25)=1,SUM('Turns'!F25),"Unknown")</f>
-        <v>0.00041875</v>
+        <v>0.000419</v>
       </c>
       <c r="S8" s="2">
+        <f>IF(COUNT('Turns'!D29)=1,SUM('Turns'!D29),"Unknown")</f>
+        <v>187.0</v>
+      </c>
+      <c r="T8" s="2">
+        <f>IF(COUNT('Turns'!E29)=1,SUM('Turns'!E29),"Unknown")</f>
+        <v>0.000197413656</v>
+      </c>
+      <c r="U8" s="2">
+        <f>IF(COUNT('Turns'!F29)=1,SUM('Turns'!F29),"Unknown")</f>
+        <v>0.0002244</v>
+      </c>
+      <c r="V8" s="2">
         <f>IF(COUNT('Turns'!D28)=1,SUM('Turns'!D28),"Unknown")</f>
-        <v>192.0</v>
-      </c>
-      <c r="T8" s="2">
+        <v>60.0</v>
+      </c>
+      <c r="W8" s="2">
         <f>IF(COUNT('Turns'!E28)=1,SUM('Turns'!E28),"Unknown")</f>
-        <v>0.00020191104</v>
-      </c>
-      <c r="U8" s="2">
+        <v>6.334128e-05</v>
+      </c>
+      <c r="X8" s="2">
         <f>IF(COUNT('Turns'!F28)=1,SUM('Turns'!F28),"Unknown")</f>
-        <v>0.0002304</v>
-      </c>
-      <c r="V8" s="2">
-        <v>0</v>
-      </c>
-      <c r="W8" s="2">
-        <v>0</v>
-      </c>
-      <c r="X8" s="2">
-        <v>0</v>
+        <v>7.2e-05</v>
       </c>
       <c r="Y8" s="2">
-        <f>IF(COUNT('Turns'!E32)=1,SUM('Turns'!E32),"Unknown")</f>
-        <v>0.0005694084125</v>
+        <f>IF(COUNT('Turns'!E33)=1,SUM('Turns'!E33),"Unknown")</f>
+        <v>0.00062989384</v>
       </c>
       <c r="Z8" s="2">
-        <f>IF(COUNT('Turns'!F32)=1,SUM('Turns'!F32),"Unknown")</f>
-        <v>0.00064975</v>
+        <f>IF(COUNT('Turns'!F33)=1,SUM('Turns'!F33),"Unknown")</f>
+        <v>0.000716</v>
       </c>
       <c r="AA8" s="5">
         <f>IF(ISNUMBER(Y8),ROUND(Y8*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>57.0</v>
+        <v>63.0</v>
       </c>
       <c r="AB8" s="5">
         <f>IF(ISNUMBER(Z8),ROUND(Z8*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>65.0</v>
+        <v>72.0</v>
       </c>
       <c r="AC8" s="1" t="s">
         <v>118</v>
       </c>
       <c r="AD8" s="1">
-        <v>3119.307</v>
+        <v>2470.494</v>
       </c>
       <c r="AE8" s="1" t="s">
         <v>133</v>
@@ -2249,7 +2285,7 @@
         <v>43</v>
       </c>
       <c r="B3" s="2">
-        <v>0.87635</v>
+        <v>0.87974</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>44</v>
